--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,26 +4106,26 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,22 +4229,22 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>6.43</v>
+        <v>1.9</v>
       </c>
       <c r="M57" t="n">
-        <v>4.09</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>4.38</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7249,10 +7249,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.83</v>
+        <v>4.22</v>
       </c>
       <c r="M85" t="n">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
       <c r="N85" t="n">
-        <v>4.42</v>
+        <v>1.84</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.22</v>
+        <v>3.88</v>
       </c>
       <c r="M87" t="n">
-        <v>4.27</v>
+        <v>3.64</v>
       </c>
       <c r="N87" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.88</v>
+        <v>1.83</v>
       </c>
       <c r="M88" t="n">
-        <v>3.64</v>
+        <v>4.12</v>
       </c>
       <c r="N88" t="n">
-        <v>2.07</v>
+        <v>4.42</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,22 +14070,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14746,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="AA120" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB120" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC120" t="n">
         <v>0</v>
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.28</v>
+        <v>5.69</v>
       </c>
       <c r="M121" t="n">
-        <v>6.3</v>
+        <v>4.37</v>
       </c>
       <c r="N121" t="n">
-        <v>13.2</v>
+        <v>1.64</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.59</v>
+        <v>2.18</v>
       </c>
       <c r="M122" t="n">
-        <v>3.86</v>
+        <v>3.15</v>
       </c>
       <c r="N122" t="n">
-        <v>2.7</v>
+        <v>3.43</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="M125" t="n">
-        <v>3.29</v>
+        <v>3.58</v>
       </c>
       <c r="N125" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="M126" t="n">
-        <v>3.58</v>
+        <v>3.29</v>
       </c>
       <c r="N126" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="M130" t="n">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="N130" t="n">
-        <v>5.19</v>
+        <v>3.11</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="M132" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="N132" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.36</v>
+        <v>1.69</v>
       </c>
       <c r="M135" t="n">
-        <v>3.41</v>
+        <v>3.83</v>
       </c>
       <c r="N135" t="n">
-        <v>2.06</v>
+        <v>4.58</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.69</v>
+        <v>1.62</v>
       </c>
       <c r="M136" t="n">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="N136" t="n">
-        <v>2.57</v>
+        <v>5.19</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>3.82</v>
+        <v>4.23</v>
       </c>
       <c r="M137" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="N137" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.55</v>
+        <v>3.42</v>
       </c>
       <c r="M141" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N141" t="n">
-        <v>5.75</v>
+        <v>1.93</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4.23</v>
+        <v>2.55</v>
       </c>
       <c r="M143" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N143" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>3.42</v>
+        <v>1.55</v>
       </c>
       <c r="M147" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N147" t="n">
-        <v>1.93</v>
+        <v>5.75</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.69</v>
+        <v>3.36</v>
       </c>
       <c r="M149" t="n">
-        <v>3.83</v>
+        <v>3.41</v>
       </c>
       <c r="N149" t="n">
-        <v>4.58</v>
+        <v>2.06</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,16 +18554,16 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD152" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,16 +19506,16 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20101,10 +20101,10 @@
         <v>0</v>
       </c>
       <c r="AA165" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB165" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M169" t="n">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="N169" t="n">
-        <v>4.37</v>
+        <v>4.62</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AA187" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB187" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.01</v>
+        <v>1.78</v>
       </c>
       <c r="M196" t="n">
-        <v>3.84</v>
+        <v>4.04</v>
       </c>
       <c r="N196" t="n">
-        <v>2.37</v>
+        <v>4.88</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB222" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.56</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.23</v>
+        <v>2.14</v>
       </c>
       <c r="M86" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="N86" t="n">
-        <v>2.36</v>
+        <v>3.64</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.88</v>
+        <v>1.83</v>
       </c>
       <c r="M87" t="n">
-        <v>3.64</v>
+        <v>4.12</v>
       </c>
       <c r="N87" t="n">
-        <v>2.07</v>
+        <v>4.42</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.83</v>
+        <v>3.23</v>
       </c>
       <c r="M88" t="n">
-        <v>4.12</v>
+        <v>3.56</v>
       </c>
       <c r="N88" t="n">
-        <v>4.42</v>
+        <v>2.36</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12485,10 +12485,10 @@
         <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,22 +13832,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.11</v>
+        <v>1.7</v>
       </c>
       <c r="M125" t="n">
-        <v>3.58</v>
+        <v>3.81</v>
       </c>
       <c r="N125" t="n">
-        <v>3.24</v>
+        <v>4.63</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="M130" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="N130" t="n">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.69</v>
+        <v>1.62</v>
       </c>
       <c r="M132" t="n">
-        <v>3.28</v>
+        <v>3.82</v>
       </c>
       <c r="N132" t="n">
-        <v>2.57</v>
+        <v>5.19</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.69</v>
+        <v>2.29</v>
       </c>
       <c r="M135" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N135" t="n">
-        <v>4.58</v>
+        <v>3.11</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>5.19</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.11</v>
+        <v>1.55</v>
       </c>
       <c r="M138" t="n">
-        <v>3.39</v>
+        <v>3.7</v>
       </c>
       <c r="N138" t="n">
-        <v>3.36</v>
+        <v>5.75</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>3.42</v>
+        <v>2.7</v>
       </c>
       <c r="M141" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N141" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,55 +17319,55 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.82</v>
+        <v>3.36</v>
       </c>
       <c r="M142" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="N142" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB142" t="n">
         <v>1.91</v>
-      </c>
-      <c r="O142" t="n">
-        <v>0</v>
-      </c>
-      <c r="P142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0</v>
-      </c>
-      <c r="S142" t="n">
-        <v>0</v>
-      </c>
-      <c r="T142" t="n">
-        <v>0</v>
-      </c>
-      <c r="U142" t="n">
-        <v>0</v>
-      </c>
-      <c r="V142" t="n">
-        <v>0</v>
-      </c>
-      <c r="W142" t="n">
-        <v>0</v>
-      </c>
-      <c r="X142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y142" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z142" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA142" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>1.78</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="M143" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="N143" t="n">
-        <v>2.55</v>
+        <v>5.22</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="M144" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N144" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.55</v>
+        <v>2.69</v>
       </c>
       <c r="M147" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="N147" t="n">
-        <v>5.75</v>
+        <v>2.57</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB147" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.36</v>
+        <v>1.69</v>
       </c>
       <c r="M149" t="n">
-        <v>3.41</v>
+        <v>3.83</v>
       </c>
       <c r="N149" t="n">
-        <v>2.06</v>
+        <v>4.58</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="M160" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="N160" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,16 +19506,16 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M169" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="N169" t="n">
-        <v>4.62</v>
+        <v>4.37</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>1.78</v>
+        <v>3.01</v>
       </c>
       <c r="M196" t="n">
-        <v>4.04</v>
+        <v>3.84</v>
       </c>
       <c r="N196" t="n">
-        <v>4.88</v>
+        <v>2.37</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB196" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>3.01</v>
+        <v>1.78</v>
       </c>
       <c r="M197" t="n">
-        <v>3.84</v>
+        <v>4.04</v>
       </c>
       <c r="N197" t="n">
-        <v>2.37</v>
+        <v>4.88</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M216" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="N216" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N217" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,17 +3273,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,14 +5062,14 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="M39" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N39" t="n">
         <v>3.36</v>
       </c>
-      <c r="N39" t="n">
-        <v>3.56</v>
-      </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6416,10 +6416,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="M84" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="N84" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB84" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1.76</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="M86" t="n">
-        <v>3.66</v>
+        <v>4.12</v>
       </c>
       <c r="N86" t="n">
-        <v>3.64</v>
+        <v>4.42</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.23</v>
+        <v>2.14</v>
       </c>
       <c r="M88" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="N88" t="n">
-        <v>2.36</v>
+        <v>3.64</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,22 +11571,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.28</v>
+        <v>2.66</v>
       </c>
       <c r="M99" t="n">
-        <v>6.3</v>
+        <v>3.44</v>
       </c>
       <c r="N99" t="n">
-        <v>13.2</v>
+        <v>2.87</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.69</v>
+        <v>1.85</v>
       </c>
       <c r="M109" t="n">
-        <v>4.37</v>
+        <v>3.2</v>
       </c>
       <c r="N109" t="n">
-        <v>1.64</v>
+        <v>4.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.13</v>
+        <v>2.92</v>
       </c>
       <c r="M111" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N111" t="n">
-        <v>3.84</v>
+        <v>2.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="M128" t="n">
-        <v>3.58</v>
+        <v>3.25</v>
       </c>
       <c r="N128" t="n">
-        <v>3.24</v>
+        <v>2.55</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="M130" t="n">
-        <v>3.39</v>
+        <v>3.64</v>
       </c>
       <c r="N130" t="n">
-        <v>3.36</v>
+        <v>5.22</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="M131" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="N131" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.62</v>
+        <v>1.41</v>
       </c>
       <c r="M132" t="n">
-        <v>3.82</v>
+        <v>4.7</v>
       </c>
       <c r="N132" t="n">
-        <v>5.19</v>
+        <v>6.88</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="M134" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.29</v>
+        <v>3.42</v>
       </c>
       <c r="M135" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N135" t="n">
-        <v>3.11</v>
+        <v>1.93</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>4.23</v>
+        <v>2.22</v>
       </c>
       <c r="M137" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="N137" t="n">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,7 +16769,7 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB137" t="n">
         <v>1.93</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>1.55</v>
+        <v>2.11</v>
       </c>
       <c r="M138" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="N138" t="n">
-        <v>5.75</v>
+        <v>3.36</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB138" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="M140" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N140" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.7</v>
+        <v>4.23</v>
       </c>
       <c r="M141" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N141" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.36</v>
+        <v>2.29</v>
       </c>
       <c r="M142" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N142" t="n">
-        <v>2.06</v>
+        <v>3.11</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.63</v>
+        <v>2.03</v>
       </c>
       <c r="M143" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="N143" t="n">
-        <v>5.22</v>
+        <v>3.48</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.55</v>
+        <v>2.83</v>
       </c>
       <c r="M144" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="N144" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.82</v>
+        <v>3.05</v>
       </c>
       <c r="M146" t="n">
-        <v>3.42</v>
+        <v>3.04</v>
       </c>
       <c r="N146" t="n">
-        <v>1.91</v>
+        <v>2.43</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="M149" t="n">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="N149" t="n">
-        <v>4.58</v>
+        <v>5.75</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,16 +18911,16 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC155" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD155" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="M157" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="N157" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,16 +19149,16 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB168" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="M172" t="n">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="N172" t="n">
-        <v>3.66</v>
+        <v>4.84</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M174" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="N174" t="n">
-        <v>4.62</v>
+        <v>4.37</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23626,13 +23626,13 @@
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -23671,10 +23671,10 @@
         <v>0</v>
       </c>
       <c r="AA195" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB195" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC195" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M203" t="n">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="N203" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="M207" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N207" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB208" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M212" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N212" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M215" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N215" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="M216" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N216" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB221" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27434,13 +27434,13 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="M227" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O227" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,22 +3039,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,17 +3154,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3280,10 +3280,10 @@
         <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="N24" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,26 +4106,26 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.13</v>
+        <v>3.65</v>
       </c>
       <c r="M38" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="N38" t="n">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="M39" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="N39" t="n">
-        <v>3.36</v>
+        <v>4.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,14 +5181,14 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="M40" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N40" t="n">
         <v>3.36</v>
       </c>
-      <c r="N40" t="n">
-        <v>3.56</v>
-      </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>4.74</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>6.43</v>
+        <v>3.29</v>
       </c>
       <c r="M49" t="n">
-        <v>4.09</v>
+        <v>3.28</v>
       </c>
       <c r="N49" t="n">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.43</v>
+        <v>1.9</v>
       </c>
       <c r="M56" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>2.07</v>
+        <v>4.38</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="M75" t="n">
-        <v>3.04</v>
+        <v>3.13</v>
       </c>
       <c r="N75" t="n">
-        <v>3.47</v>
+        <v>3.66</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.98</v>
+        <v>2.35</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N80" t="n">
-        <v>2.1</v>
+        <v>4.89</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="M82" t="n">
-        <v>3.46</v>
+        <v>2.8</v>
       </c>
       <c r="N82" t="n">
-        <v>4.43</v>
+        <v>3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="M83" t="n">
-        <v>3.64</v>
+        <v>4.27</v>
       </c>
       <c r="N83" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="M84" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="N84" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="M93" t="n">
-        <v>3.86</v>
+        <v>3.44</v>
       </c>
       <c r="N93" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="M100" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N100" t="n">
-        <v>3.84</v>
+        <v>3.43</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -12961,10 +12961,10 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="M106" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="N106" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.85</v>
+        <v>5.69</v>
       </c>
       <c r="M109" t="n">
-        <v>3.2</v>
+        <v>4.37</v>
       </c>
       <c r="N109" t="n">
-        <v>4.5</v>
+        <v>1.64</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>5.69</v>
+        <v>1.79</v>
       </c>
       <c r="M124" t="n">
-        <v>4.37</v>
+        <v>3.4</v>
       </c>
       <c r="N124" t="n">
-        <v>1.64</v>
+        <v>4.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15222,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>0</v>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.69</v>
+        <v>2.7</v>
       </c>
       <c r="M126" t="n">
-        <v>3.83</v>
+        <v>3.1</v>
       </c>
       <c r="N126" t="n">
-        <v>4.58</v>
+        <v>2.5</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.55</v>
+        <v>2.03</v>
       </c>
       <c r="M128" t="n">
-        <v>3.25</v>
+        <v>3.48</v>
       </c>
       <c r="N128" t="n">
-        <v>2.55</v>
+        <v>3.48</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="M129" t="n">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="N129" t="n">
-        <v>4.63</v>
+        <v>5.22</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.63</v>
+        <v>3.05</v>
       </c>
       <c r="M130" t="n">
-        <v>3.64</v>
+        <v>3.04</v>
       </c>
       <c r="N130" t="n">
-        <v>5.22</v>
+        <v>2.43</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>3.36</v>
+        <v>2.83</v>
       </c>
       <c r="M131" t="n">
-        <v>3.41</v>
+        <v>3.24</v>
       </c>
       <c r="N131" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="M132" t="n">
-        <v>4.7</v>
+        <v>3.81</v>
       </c>
       <c r="N132" t="n">
-        <v>6.88</v>
+        <v>4.63</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AB132" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>3.82</v>
+        <v>2.19</v>
       </c>
       <c r="M134" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="N134" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>3.42</v>
+        <v>2.55</v>
       </c>
       <c r="M135" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N135" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="M136" t="n">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="N136" t="n">
-        <v>2.5</v>
+        <v>2.06</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.22</v>
+        <v>2.69</v>
       </c>
       <c r="M137" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="N137" t="n">
-        <v>3.05</v>
+        <v>2.57</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.11</v>
+        <v>3.82</v>
       </c>
       <c r="M138" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="N138" t="n">
-        <v>3.36</v>
+        <v>1.91</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16891,7 +16891,7 @@
         <v>1.98</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.11</v>
+        <v>4.23</v>
       </c>
       <c r="M139" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="N139" t="n">
-        <v>3.24</v>
+        <v>1.79</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="M140" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N140" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>4.23</v>
+        <v>2.22</v>
       </c>
       <c r="M141" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="N141" t="n">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,7 +17245,7 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB141" t="n">
         <v>1.93</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.29</v>
+        <v>1.41</v>
       </c>
       <c r="M142" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="N142" t="n">
-        <v>3.11</v>
+        <v>6.88</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2.01</v>
+        <v>1.57</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="M143" t="n">
-        <v>3.48</v>
+        <v>3.58</v>
       </c>
       <c r="N143" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="M144" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="N144" t="n">
-        <v>2.44</v>
+        <v>3.11</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M145" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="N145" t="n">
-        <v>4.78</v>
+        <v>5.19</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.05</v>
+        <v>1.69</v>
       </c>
       <c r="M146" t="n">
-        <v>3.04</v>
+        <v>3.83</v>
       </c>
       <c r="N146" t="n">
-        <v>2.43</v>
+        <v>4.58</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.62</v>
+        <v>3.42</v>
       </c>
       <c r="M148" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="N148" t="n">
-        <v>5.19</v>
+        <v>1.93</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="M149" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N149" t="n">
-        <v>5.75</v>
+        <v>4.78</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18743,17 +18743,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,16 +18792,16 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC154" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N155" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,16 +18911,16 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD155" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="M159" t="n">
-        <v>5.65</v>
+        <v>5.23</v>
       </c>
       <c r="N159" t="n">
-        <v>14.7</v>
+        <v>7.75</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M166" t="n">
-        <v>4.55</v>
+        <v>4.12</v>
       </c>
       <c r="N166" t="n">
-        <v>6.05</v>
+        <v>4.62</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21291,10 +21291,10 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB175" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC175" t="n">
         <v>0</v>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4.26</v>
+        <v>2.13</v>
       </c>
       <c r="M191" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="N191" t="n">
-        <v>1.7</v>
+        <v>3.22</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.68</v>
+        <v>1.78</v>
       </c>
       <c r="M199" t="n">
-        <v>3.17</v>
+        <v>4.04</v>
       </c>
       <c r="N199" t="n">
-        <v>2.83</v>
+        <v>4.88</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.78</v>
+        <v>2.68</v>
       </c>
       <c r="M200" t="n">
-        <v>4.04</v>
+        <v>3.17</v>
       </c>
       <c r="N200" t="n">
-        <v>4.88</v>
+        <v>2.83</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="M203" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N203" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M207" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="N207" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25218,10 +25218,10 @@
         <v>0</v>
       </c>
       <c r="AA208" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB208" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC208" t="n">
         <v>0</v>
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.77</v>
+        <v>3.39</v>
       </c>
       <c r="M209" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N209" t="n">
-        <v>3.97</v>
+        <v>1.95</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>3.39</v>
+        <v>2.3</v>
       </c>
       <c r="M210" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="N210" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="M211" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N211" t="n">
-        <v>2.91</v>
+        <v>3.97</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="M212" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="N212" t="n">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="M214" t="n">
-        <v>3.96</v>
+        <v>3.79</v>
       </c>
       <c r="N214" t="n">
-        <v>5.16</v>
+        <v>4.37</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="M215" t="n">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="N215" t="n">
-        <v>4.17</v>
+        <v>2.38</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.57</v>
+        <v>1.79</v>
       </c>
       <c r="M216" t="n">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="N216" t="n">
-        <v>2.38</v>
+        <v>4.17</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="M217" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="N217" t="n">
-        <v>4.37</v>
+        <v>5.16</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="M219" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="N219" t="n">
-        <v>4.32</v>
+        <v>2.38</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="M220" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N220" t="n">
-        <v>2.38</v>
+        <v>4.32</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="M223" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="N223" t="n">
-        <v>3.24</v>
+        <v>2.56</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="M39" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>4.74</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="M40" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="N40" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>3.56</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="M43" t="n">
-        <v>3.36</v>
+        <v>3.84</v>
       </c>
       <c r="N43" t="n">
-        <v>3.56</v>
+        <v>4.74</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>6.43</v>
+        <v>3.29</v>
       </c>
       <c r="M52" t="n">
-        <v>4.09</v>
+        <v>3.28</v>
       </c>
       <c r="N52" t="n">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6654,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.22</v>
+        <v>1.81</v>
       </c>
       <c r="M72" t="n">
-        <v>3.04</v>
+        <v>3.46</v>
       </c>
       <c r="N72" t="n">
-        <v>3.47</v>
+        <v>4.43</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="M80" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N80" t="n">
-        <v>4.89</v>
+        <v>3</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
         <v>2.25</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="M82" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="N82" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.22</v>
+        <v>1.83</v>
       </c>
       <c r="M83" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="N83" t="n">
-        <v>1.84</v>
+        <v>4.42</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="M84" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="N84" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB84" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>1.76</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.83</v>
+        <v>3.88</v>
       </c>
       <c r="M86" t="n">
-        <v>4.12</v>
+        <v>3.64</v>
       </c>
       <c r="N86" t="n">
-        <v>4.42</v>
+        <v>2.07</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,22 +12880,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>5.69</v>
+        <v>3.6</v>
       </c>
       <c r="M109" t="n">
-        <v>4.37</v>
+        <v>3.5</v>
       </c>
       <c r="N109" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13437,10 +13437,10 @@
         <v>0</v>
       </c>
       <c r="AA109" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.92</v>
+        <v>2.59</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>3.86</v>
       </c>
       <c r="N119" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="M125" t="n">
-        <v>3.7</v>
+        <v>3.29</v>
       </c>
       <c r="N125" t="n">
-        <v>5.75</v>
+        <v>3.12</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="M126" t="n">
-        <v>3.1</v>
+        <v>3.81</v>
       </c>
       <c r="N126" t="n">
-        <v>2.5</v>
+        <v>4.63</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.03</v>
+        <v>3.82</v>
       </c>
       <c r="M128" t="n">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="N128" t="n">
-        <v>3.48</v>
+        <v>1.91</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>5.22</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.05</v>
+        <v>1.63</v>
       </c>
       <c r="M130" t="n">
-        <v>3.04</v>
+        <v>4.1</v>
       </c>
       <c r="N130" t="n">
-        <v>2.43</v>
+        <v>4.78</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.83</v>
+        <v>1.62</v>
       </c>
       <c r="M131" t="n">
-        <v>3.24</v>
+        <v>3.82</v>
       </c>
       <c r="N131" t="n">
-        <v>2.44</v>
+        <v>5.19</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="M132" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="N132" t="n">
-        <v>4.63</v>
+        <v>3.48</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB132" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.29</v>
+        <v>4.23</v>
       </c>
       <c r="M133" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N133" t="n">
-        <v>3.12</v>
+        <v>1.79</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="M134" t="n">
-        <v>3.3</v>
+        <v>3.39</v>
       </c>
       <c r="N134" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.55</v>
+        <v>1.69</v>
       </c>
       <c r="M135" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="N135" t="n">
-        <v>2.55</v>
+        <v>4.58</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.36</v>
+        <v>1.55</v>
       </c>
       <c r="M136" t="n">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="N136" t="n">
-        <v>2.06</v>
+        <v>5.75</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="M137" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="N137" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>3.82</v>
+        <v>2.7</v>
       </c>
       <c r="M138" t="n">
-        <v>3.42</v>
+        <v>3.1</v>
       </c>
       <c r="N138" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>4.23</v>
+        <v>3.36</v>
       </c>
       <c r="M139" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="N139" t="n">
-        <v>1.79</v>
+        <v>2.06</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N140" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="M141" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="N141" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.93</v>
+        <v>1.7</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.41</v>
+        <v>2.11</v>
       </c>
       <c r="M142" t="n">
-        <v>4.7</v>
+        <v>3.58</v>
       </c>
       <c r="N142" t="n">
-        <v>6.88</v>
+        <v>3.24</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.11</v>
+        <v>1.41</v>
       </c>
       <c r="M143" t="n">
-        <v>3.58</v>
+        <v>4.7</v>
       </c>
       <c r="N143" t="n">
-        <v>3.24</v>
+        <v>6.88</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="M144" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="N144" t="n">
-        <v>3.11</v>
+        <v>5.22</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.62</v>
+        <v>3.42</v>
       </c>
       <c r="M145" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="N145" t="n">
-        <v>5.19</v>
+        <v>1.93</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="M146" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N146" t="n">
-        <v>4.58</v>
+        <v>2.55</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,55 +18033,55 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.42</v>
+        <v>2.22</v>
       </c>
       <c r="M148" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="N148" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB148" t="n">
         <v>1.93</v>
-      </c>
-      <c r="O148" t="n">
-        <v>0</v>
-      </c>
-      <c r="P148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0</v>
-      </c>
-      <c r="S148" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" t="n">
-        <v>0</v>
-      </c>
-      <c r="V148" t="n">
-        <v>0</v>
-      </c>
-      <c r="W148" t="n">
-        <v>0</v>
-      </c>
-      <c r="X148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y148" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z148" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA148" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB148" t="n">
-        <v>1.84</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.63</v>
+        <v>2.83</v>
       </c>
       <c r="M149" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="N149" t="n">
-        <v>4.78</v>
+        <v>2.44</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18743,17 +18743,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,16 +18792,16 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD154" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18981,17 +18981,17 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,16 +19030,16 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD156" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="M160" t="n">
-        <v>5.65</v>
+        <v>5.23</v>
       </c>
       <c r="N160" t="n">
-        <v>14.7</v>
+        <v>7.75</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M166" t="n">
-        <v>4.12</v>
+        <v>3.14</v>
       </c>
       <c r="N166" t="n">
-        <v>4.62</v>
+        <v>3.66</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="M174" t="n">
-        <v>3.76</v>
+        <v>4.55</v>
       </c>
       <c r="N174" t="n">
-        <v>4.37</v>
+        <v>6.05</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.13</v>
+        <v>4.8</v>
       </c>
       <c r="M191" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N191" t="n">
-        <v>3.22</v>
+        <v>1.9</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB191" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>2.68</v>
+        <v>1.78</v>
       </c>
       <c r="M200" t="n">
-        <v>3.17</v>
+        <v>4.04</v>
       </c>
       <c r="N200" t="n">
-        <v>2.83</v>
+        <v>4.88</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="M203" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="N203" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="M205" t="n">
-        <v>3.54</v>
+        <v>3.68</v>
       </c>
       <c r="N205" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.39</v>
+        <v>2.42</v>
       </c>
       <c r="M209" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N209" t="n">
-        <v>1.95</v>
+        <v>2.91</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25337,10 +25337,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.77</v>
+        <v>3.39</v>
       </c>
       <c r="M211" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N211" t="n">
-        <v>3.97</v>
+        <v>1.95</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="M212" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N212" t="n">
-        <v>2.91</v>
+        <v>3.97</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.64</v>
+        <v>1.82</v>
       </c>
       <c r="M213" t="n">
-        <v>3.68</v>
+        <v>3.79</v>
       </c>
       <c r="N213" t="n">
-        <v>4.62</v>
+        <v>4.37</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.82</v>
+        <v>2.57</v>
       </c>
       <c r="M214" t="n">
-        <v>3.79</v>
+        <v>3.34</v>
       </c>
       <c r="N214" t="n">
-        <v>4.37</v>
+        <v>2.38</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="M215" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N215" t="n">
-        <v>2.38</v>
+        <v>4.62</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="M216" t="n">
-        <v>3.72</v>
+        <v>3.96</v>
       </c>
       <c r="N216" t="n">
-        <v>4.17</v>
+        <v>5.16</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="M217" t="n">
-        <v>3.96</v>
+        <v>3.72</v>
       </c>
       <c r="N217" t="n">
-        <v>5.16</v>
+        <v>4.17</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N224" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB225" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.08</v>
+        <v>2.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="M40" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="M41" t="n">
-        <v>3.36</v>
+        <v>3.84</v>
       </c>
       <c r="N41" t="n">
-        <v>3.56</v>
+        <v>4.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.68</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>3.84</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>4.74</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB43" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
+        <v>3.43</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N53" t="n">
-        <v>4.38</v>
+        <v>2.07</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.81</v>
+        <v>2.11</v>
       </c>
       <c r="M72" t="n">
-        <v>3.46</v>
+        <v>3.13</v>
       </c>
       <c r="N72" t="n">
-        <v>4.43</v>
+        <v>3.66</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>4.22</v>
+        <v>3.23</v>
       </c>
       <c r="M85" t="n">
-        <v>4.27</v>
+        <v>3.56</v>
       </c>
       <c r="N85" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,14 +10655,14 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.88</v>
+        <v>2.14</v>
       </c>
       <c r="M86" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="N86" t="n">
         <v>3.64</v>
       </c>
-      <c r="N86" t="n">
-        <v>2.07</v>
-      </c>
       <c r="O86" t="n">
         <v>0</v>
       </c>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.14</v>
+        <v>4.22</v>
       </c>
       <c r="M88" t="n">
-        <v>3.66</v>
+        <v>4.27</v>
       </c>
       <c r="N88" t="n">
-        <v>3.64</v>
+        <v>1.84</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N92" t="n">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5.52</v>
+        <v>3.6</v>
       </c>
       <c r="M99" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N99" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.18</v>
+        <v>1.98</v>
       </c>
       <c r="M100" t="n">
-        <v>3.15</v>
+        <v>3.63</v>
       </c>
       <c r="N100" t="n">
-        <v>3.43</v>
+        <v>3.77</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,22 +12404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13392,13 +13392,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,55 +13630,55 @@
         </is>
       </c>
       <c r="L111" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB111" t="n">
         <v>1.85</v>
-      </c>
-      <c r="M111" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N111" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13913,10 +13913,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="M118" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>3.77</v>
+        <v>4.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.59</v>
+        <v>1.28</v>
       </c>
       <c r="M119" t="n">
-        <v>3.86</v>
+        <v>6.3</v>
       </c>
       <c r="N119" t="n">
-        <v>2.7</v>
+        <v>13.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.29</v>
+        <v>2.83</v>
       </c>
       <c r="M125" t="n">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="N125" t="n">
-        <v>3.12</v>
+        <v>2.44</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="M126" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="N126" t="n">
-        <v>4.63</v>
+        <v>5.75</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB126" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="M127" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="N127" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>2.01</v>
+        <v>1.77</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="M128" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="N128" t="n">
-        <v>1.91</v>
+        <v>3.36</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15701,7 +15701,7 @@
         <v>1.98</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="M132" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>3.48</v>
+        <v>3.11</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>4.23</v>
+        <v>1.63</v>
       </c>
       <c r="M133" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N133" t="n">
-        <v>1.79</v>
+        <v>4.78</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.11</v>
+        <v>1.41</v>
       </c>
       <c r="M134" t="n">
-        <v>3.39</v>
+        <v>4.7</v>
       </c>
       <c r="N134" t="n">
-        <v>3.36</v>
+        <v>6.88</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.69</v>
+        <v>4.23</v>
       </c>
       <c r="M135" t="n">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="N135" t="n">
-        <v>4.58</v>
+        <v>1.79</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="M136" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N136" t="n">
-        <v>5.75</v>
+        <v>2.43</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>3.05</v>
+        <v>3.36</v>
       </c>
       <c r="M137" t="n">
-        <v>3.04</v>
+        <v>3.41</v>
       </c>
       <c r="N137" t="n">
-        <v>2.43</v>
+        <v>2.06</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.7</v>
+        <v>2.29</v>
       </c>
       <c r="M138" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="N138" t="n">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N139" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="M141" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N141" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.11</v>
+        <v>3.82</v>
       </c>
       <c r="M142" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="N142" t="n">
-        <v>3.24</v>
+        <v>1.91</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.41</v>
+        <v>2.55</v>
       </c>
       <c r="M143" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="N143" t="n">
-        <v>6.88</v>
+        <v>2.55</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M144" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="N144" t="n">
-        <v>5.22</v>
+        <v>4.58</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>3.42</v>
+        <v>2.69</v>
       </c>
       <c r="M145" t="n">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="N145" t="n">
-        <v>1.93</v>
+        <v>2.57</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="M146" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="N146" t="n">
-        <v>2.55</v>
+        <v>3.24</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="M147" t="n">
-        <v>3.28</v>
+        <v>3.81</v>
       </c>
       <c r="N147" t="n">
-        <v>2.57</v>
+        <v>4.63</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB147" t="n">
         <v>2</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>1.79</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="M148" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="N148" t="n">
-        <v>3.05</v>
+        <v>5.22</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="M149" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="N149" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18981,17 +18981,17 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19030,16 +19030,16 @@
         <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD156" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="M157" t="n">
-        <v>5.65</v>
+        <v>5.23</v>
       </c>
       <c r="N157" t="n">
-        <v>14.7</v>
+        <v>7.75</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19219,17 +19219,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.28</v>
+        <v>1.21</v>
       </c>
       <c r="M158" t="n">
-        <v>3.14</v>
+        <v>5</v>
       </c>
       <c r="N158" t="n">
-        <v>2.46</v>
+        <v>6.5</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="M169" t="n">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="N169" t="n">
-        <v>4.37</v>
+        <v>4.62</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="M174" t="n">
-        <v>4.55</v>
+        <v>3.78</v>
       </c>
       <c r="N174" t="n">
-        <v>6.05</v>
+        <v>4.84</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="M175" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="N175" t="n">
-        <v>4.84</v>
+        <v>3.66</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21291,10 +21291,10 @@
         <v>0</v>
       </c>
       <c r="AA175" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB175" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC175" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22075,7 +22075,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.13</v>
+        <v>4.26</v>
       </c>
       <c r="M188" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="N188" t="n">
-        <v>3.22</v>
+        <v>1.7</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M191" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="N191" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB191" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.68</v>
+        <v>3.01</v>
       </c>
       <c r="M196" t="n">
-        <v>3.17</v>
+        <v>3.84</v>
       </c>
       <c r="N196" t="n">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>3.01</v>
+        <v>2.68</v>
       </c>
       <c r="M198" t="n">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
       <c r="N198" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB201" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="M205" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N205" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M206" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N206" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB207" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>2.42</v>
+        <v>3.39</v>
       </c>
       <c r="M209" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N209" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25337,10 +25337,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="M210" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="N210" t="n">
-        <v>3.7</v>
+        <v>2.91</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.39</v>
+        <v>2.3</v>
       </c>
       <c r="M211" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="N211" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M213" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="N213" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="M214" t="n">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="N214" t="n">
-        <v>2.38</v>
+        <v>5.16</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="M215" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N215" t="n">
-        <v>4.62</v>
+        <v>2.38</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB215" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M216" t="n">
-        <v>3.96</v>
+        <v>3.68</v>
       </c>
       <c r="N216" t="n">
-        <v>5.16</v>
+        <v>4.62</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="M217" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="N217" t="n">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G233" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,17 +3868,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>3.36</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.65</v>
+        <v>2.04</v>
       </c>
       <c r="M39" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>2.06</v>
+        <v>3.56</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="N40" t="n">
-        <v>3.56</v>
+        <v>2.06</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.43</v>
+        <v>1.9</v>
       </c>
       <c r="M53" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N53" t="n">
-        <v>2.07</v>
+        <v>4.38</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.6</v>
+        <v>2.11</v>
       </c>
       <c r="M69" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="N69" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.83</v>
+        <v>4.22</v>
       </c>
       <c r="M83" t="n">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
       <c r="N83" t="n">
-        <v>4.42</v>
+        <v>1.84</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10381,7 +10381,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.42</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.14</v>
+        <v>3.88</v>
       </c>
       <c r="M86" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="N86" t="n">
-        <v>3.64</v>
+        <v>2.07</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.88</v>
+        <v>3.23</v>
       </c>
       <c r="M87" t="n">
-        <v>3.64</v>
+        <v>3.56</v>
       </c>
       <c r="N87" t="n">
-        <v>2.07</v>
+        <v>2.36</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB87" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>1.76</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>4.22</v>
+        <v>2.14</v>
       </c>
       <c r="M88" t="n">
-        <v>4.27</v>
+        <v>3.66</v>
       </c>
       <c r="N88" t="n">
-        <v>1.84</v>
+        <v>3.64</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.59</v>
+        <v>5.69</v>
       </c>
       <c r="M90" t="n">
-        <v>3.86</v>
+        <v>4.37</v>
       </c>
       <c r="N90" t="n">
-        <v>2.7</v>
+        <v>1.64</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.92</v>
+        <v>5.52</v>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>3.92</v>
       </c>
       <c r="N91" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="M92" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="N92" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="M93" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N93" t="n">
-        <v>3.43</v>
+        <v>3.84</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11809,22 +11809,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>5.69</v>
+        <v>2.59</v>
       </c>
       <c r="M98" t="n">
-        <v>4.37</v>
+        <v>3.86</v>
       </c>
       <c r="N98" t="n">
-        <v>1.64</v>
+        <v>2.7</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13511,13 +13511,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -13556,10 +13556,10 @@
         <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="M115" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N115" t="n">
-        <v>2.87</v>
+        <v>1.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14151,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="AA115" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="M118" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N118" t="n">
         <v>4.5</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14627,10 +14627,10 @@
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB119" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="M125" t="n">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="N125" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="M126" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="N126" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB126" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="M127" t="n">
-        <v>3.46</v>
+        <v>4.1</v>
       </c>
       <c r="N127" t="n">
-        <v>3.05</v>
+        <v>4.78</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="M128" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="N128" t="n">
-        <v>3.36</v>
+        <v>3.11</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.62</v>
+        <v>2.11</v>
       </c>
       <c r="M131" t="n">
-        <v>3.82</v>
+        <v>3.39</v>
       </c>
       <c r="N131" t="n">
-        <v>5.19</v>
+        <v>3.36</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="N132" t="n">
-        <v>3.11</v>
+        <v>3.24</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="M133" t="n">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
       <c r="N133" t="n">
-        <v>4.78</v>
+        <v>4.63</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.41</v>
+        <v>2.83</v>
       </c>
       <c r="M134" t="n">
-        <v>4.7</v>
+        <v>3.24</v>
       </c>
       <c r="N134" t="n">
-        <v>6.88</v>
+        <v>2.44</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB134" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.23</v>
+        <v>2.55</v>
       </c>
       <c r="M135" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N135" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>3.05</v>
+        <v>2.19</v>
       </c>
       <c r="M136" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="N136" t="n">
-        <v>2.43</v>
+        <v>3.25</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>3.36</v>
+        <v>2.7</v>
       </c>
       <c r="M137" t="n">
-        <v>3.41</v>
+        <v>3.1</v>
       </c>
       <c r="N137" t="n">
-        <v>2.06</v>
+        <v>2.5</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.29</v>
+        <v>3.05</v>
       </c>
       <c r="M138" t="n">
-        <v>3.29</v>
+        <v>3.04</v>
       </c>
       <c r="N138" t="n">
-        <v>3.12</v>
+        <v>2.43</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>4.23</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.42</v>
+        <v>1.55</v>
       </c>
       <c r="M140" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N140" t="n">
-        <v>1.93</v>
+        <v>5.75</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="M141" t="n">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="N141" t="n">
-        <v>2.5</v>
+        <v>4.58</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.82</v>
+        <v>2.69</v>
       </c>
       <c r="M142" t="n">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="N142" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.55</v>
+        <v>3.42</v>
       </c>
       <c r="M143" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N143" t="n">
-        <v>2.55</v>
+        <v>1.93</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.69</v>
+        <v>3.82</v>
       </c>
       <c r="M144" t="n">
-        <v>3.83</v>
+        <v>3.42</v>
       </c>
       <c r="N144" t="n">
-        <v>4.58</v>
+        <v>1.91</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N145" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N146" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="M147" t="n">
-        <v>3.81</v>
+        <v>3.64</v>
       </c>
       <c r="N147" t="n">
-        <v>4.63</v>
+        <v>5.22</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="M148" t="n">
-        <v>3.64</v>
+        <v>4.7</v>
       </c>
       <c r="N148" t="n">
-        <v>5.22</v>
+        <v>6.88</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.19</v>
+        <v>3.36</v>
       </c>
       <c r="M149" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N149" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18505,17 +18505,17 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,16 +18554,16 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC152" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD152" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19219,17 +19219,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N159" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19631,10 +19631,10 @@
         <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M169" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="N169" t="n">
-        <v>4.62</v>
+        <v>4.37</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="M171" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="N171" t="n">
-        <v>4.37</v>
+        <v>4.84</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AB171" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="M186" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N186" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB190" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>4.8</v>
+        <v>2.13</v>
       </c>
       <c r="M194" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="N194" t="n">
-        <v>1.9</v>
+        <v>3.22</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1.78</v>
+        <v>2.68</v>
       </c>
       <c r="M201" t="n">
-        <v>4.04</v>
+        <v>3.17</v>
       </c>
       <c r="N201" t="n">
-        <v>4.88</v>
+        <v>2.83</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24385,10 +24385,10 @@
         <v>0</v>
       </c>
       <c r="AA201" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB204" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M206" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.05</v>
+        <v>2.68</v>
       </c>
       <c r="M207" t="n">
-        <v>3.68</v>
+        <v>3.14</v>
       </c>
       <c r="N207" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25099,10 +25099,10 @@
         <v>0</v>
       </c>
       <c r="AA207" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB207" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="M208" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N208" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M211" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="N211" t="n">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M212" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="N212" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="M213" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="N213" t="n">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="M215" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N215" t="n">
-        <v>2.38</v>
+        <v>4.62</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26051,10 +26051,10 @@
         <v>0</v>
       </c>
       <c r="AA215" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB215" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC215" t="n">
         <v>0</v>
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="M216" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N216" t="n">
-        <v>4.62</v>
+        <v>2.38</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB216" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M217" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="N217" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="M219" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N219" t="n">
-        <v>2.38</v>
+        <v>4.32</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="M220" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="N220" t="n">
-        <v>4.32</v>
+        <v>2.38</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="M224" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="N224" t="n">
-        <v>3.24</v>
+        <v>2.56</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,17 +3868,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="M33" t="n">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="N33" t="n">
-        <v>4.31</v>
+        <v>3.83</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="N39" t="n">
-        <v>3.56</v>
+        <v>2.06</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="N42" t="n">
-        <v>3.35</v>
+        <v>3.56</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.9</v>
+        <v>3.43</v>
       </c>
       <c r="M53" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N53" t="n">
-        <v>4.38</v>
+        <v>2.07</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>6.43</v>
+        <v>1.9</v>
       </c>
       <c r="M56" t="n">
-        <v>4.09</v>
+        <v>3.2</v>
       </c>
       <c r="N56" t="n">
-        <v>1.41</v>
+        <v>4.38</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7130,10 +7130,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.43</v>
+        <v>1.79</v>
       </c>
       <c r="M57" t="n">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="N57" t="n">
-        <v>2.07</v>
+        <v>4.68</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.93</v>
+        <v>3.6</v>
       </c>
       <c r="M70" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>4.89</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="M79" t="n">
-        <v>2.8</v>
+        <v>3.46</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>4.43</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -9941,13 +9941,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>4.22</v>
+        <v>2.14</v>
       </c>
       <c r="M83" t="n">
-        <v>4.27</v>
+        <v>3.66</v>
       </c>
       <c r="N83" t="n">
-        <v>1.84</v>
+        <v>3.64</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.83</v>
+        <v>4.22</v>
       </c>
       <c r="M84" t="n">
-        <v>4.12</v>
+        <v>4.27</v>
       </c>
       <c r="N84" t="n">
-        <v>4.42</v>
+        <v>1.84</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="M87" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="N87" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="M88" t="n">
-        <v>3.66</v>
+        <v>4.12</v>
       </c>
       <c r="N88" t="n">
-        <v>3.64</v>
+        <v>4.42</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11414,10 +11414,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N94" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="M96" t="n">
-        <v>3.44</v>
+        <v>3.86</v>
       </c>
       <c r="N96" t="n">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="M122" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="N122" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="M125" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
       <c r="N125" t="n">
-        <v>3.12</v>
+        <v>3.36</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="M126" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="N126" t="n">
-        <v>3.05</v>
+        <v>5.22</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.63</v>
+        <v>2.83</v>
       </c>
       <c r="M127" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="N127" t="n">
-        <v>4.78</v>
+        <v>2.44</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M128" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N128" t="n">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,55 +15772,55 @@
         </is>
       </c>
       <c r="L129" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M129" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N129" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB129" t="n">
         <v>2.03</v>
-      </c>
-      <c r="M129" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="N129" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>1.8</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
       <c r="M130" t="n">
-        <v>3.82</v>
+        <v>3.29</v>
       </c>
       <c r="N130" t="n">
-        <v>5.19</v>
+        <v>3.12</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="M131" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
       <c r="N131" t="n">
-        <v>3.36</v>
+        <v>2.57</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.11</v>
+        <v>5.67</v>
       </c>
       <c r="M132" t="n">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="N132" t="n">
-        <v>3.24</v>
+        <v>1.56</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="M133" t="n">
-        <v>3.81</v>
+        <v>3.48</v>
       </c>
       <c r="N133" t="n">
-        <v>4.63</v>
+        <v>3.48</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AB133" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.83</v>
+        <v>1.82</v>
       </c>
       <c r="M134" t="n">
-        <v>3.24</v>
+        <v>3.62</v>
       </c>
       <c r="N134" t="n">
-        <v>2.44</v>
+        <v>4.04</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB134" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.55</v>
+        <v>4.23</v>
       </c>
       <c r="M135" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N135" t="n">
-        <v>2.55</v>
+        <v>1.79</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.7</v>
+        <v>1.41</v>
       </c>
       <c r="M137" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="N137" t="n">
-        <v>2.5</v>
+        <v>6.88</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>3.05</v>
+        <v>2.29</v>
       </c>
       <c r="M138" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N138" t="n">
-        <v>2.43</v>
+        <v>3.11</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>4.23</v>
+        <v>2.11</v>
       </c>
       <c r="M139" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="N139" t="n">
-        <v>1.79</v>
+        <v>3.24</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.55</v>
+        <v>2.22</v>
       </c>
       <c r="M140" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="N140" t="n">
-        <v>5.75</v>
+        <v>3.05</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="M141" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="N141" t="n">
-        <v>4.58</v>
+        <v>5.19</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2.69</v>
+        <v>3.05</v>
       </c>
       <c r="M142" t="n">
-        <v>3.28</v>
+        <v>3.04</v>
       </c>
       <c r="N142" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="M143" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="N143" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M146" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17917,10 +17917,10 @@
         <v>1.63</v>
       </c>
       <c r="M147" t="n">
-        <v>3.64</v>
+        <v>4.1</v>
       </c>
       <c r="N147" t="n">
-        <v>5.22</v>
+        <v>4.78</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="M148" t="n">
-        <v>4.7</v>
+        <v>3.83</v>
       </c>
       <c r="N148" t="n">
-        <v>6.88</v>
+        <v>4.58</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="M149" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N149" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18505,17 +18505,17 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18554,16 +18554,16 @@
         <v>0</v>
       </c>
       <c r="AA152" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB152" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD152" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M155" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18917,10 +18917,10 @@
         <v>0</v>
       </c>
       <c r="AC155" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD155" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19219,17 +19219,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19631,10 +19631,10 @@
         <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N168" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="M171" t="n">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N171" t="n">
-        <v>4.84</v>
+        <v>4.62</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21837,7 +21837,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M186" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="N186" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M187" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23076,10 +23076,10 @@
         <v>0</v>
       </c>
       <c r="AA190" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB190" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.01</v>
+        <v>2.68</v>
       </c>
       <c r="M196" t="n">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
       <c r="N196" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N200" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB200" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N203" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24742,10 +24742,10 @@
         <v>0</v>
       </c>
       <c r="AA204" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB204" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB205" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="M206" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N206" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.68</v>
+        <v>2.06</v>
       </c>
       <c r="M207" t="n">
-        <v>3.14</v>
+        <v>3.54</v>
       </c>
       <c r="N207" t="n">
-        <v>2.63</v>
+        <v>3.81</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M208" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N208" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M211" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="N211" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M212" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="N212" t="n">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M213" t="n">
-        <v>3.79</v>
+        <v>3.72</v>
       </c>
       <c r="N213" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.53</v>
+        <v>2.57</v>
       </c>
       <c r="M214" t="n">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
       <c r="N214" t="n">
-        <v>5.16</v>
+        <v>2.38</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="M215" t="n">
-        <v>3.68</v>
+        <v>3.96</v>
       </c>
       <c r="N215" t="n">
-        <v>4.62</v>
+        <v>5.16</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>2.57</v>
+        <v>1.82</v>
       </c>
       <c r="M216" t="n">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
       <c r="N216" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26170,10 +26170,10 @@
         <v>0</v>
       </c>
       <c r="AA216" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB216" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC216" t="n">
         <v>0</v>
@@ -26208,7 +26208,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="M217" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="N217" t="n">
-        <v>4.17</v>
+        <v>4.62</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="M219" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="N219" t="n">
-        <v>4.32</v>
+        <v>2.38</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="M220" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N220" t="n">
-        <v>2.38</v>
+        <v>4.32</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="M221" t="n">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="N221" t="n">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="M222" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="N222" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,26 +3035,26 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>3.36</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M38" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="N38" t="n">
-        <v>3.36</v>
+        <v>3.56</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3.65</v>
+        <v>1.68</v>
       </c>
       <c r="M39" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="N39" t="n">
-        <v>2.06</v>
+        <v>4.74</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.68</v>
+        <v>2.45</v>
       </c>
       <c r="M41" t="n">
-        <v>3.84</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>4.74</v>
+        <v>2.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>3.56</v>
+        <v>3.35</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>3.65</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="N43" t="n">
-        <v>3.35</v>
+        <v>2.06</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.29</v>
+        <v>1.79</v>
       </c>
       <c r="M44" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>4.68</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6535,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>3.53</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.14</v>
+        <v>3.23</v>
       </c>
       <c r="M83" t="n">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="N83" t="n">
-        <v>3.64</v>
+        <v>2.36</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.88</v>
+        <v>1.83</v>
       </c>
       <c r="M87" t="n">
-        <v>3.64</v>
+        <v>4.12</v>
       </c>
       <c r="N87" t="n">
-        <v>2.07</v>
+        <v>4.42</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="M88" t="n">
-        <v>4.12</v>
+        <v>3.66</v>
       </c>
       <c r="N88" t="n">
-        <v>4.42</v>
+        <v>3.64</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AB88" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,22 +11452,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12009,10 +12009,10 @@
         <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.13</v>
+        <v>5.52</v>
       </c>
       <c r="M100" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="N100" t="n">
-        <v>3.84</v>
+        <v>1.57</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,22 +12642,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.69</v>
+        <v>1.28</v>
       </c>
       <c r="M111" t="n">
-        <v>4.37</v>
+        <v>6.3</v>
       </c>
       <c r="N111" t="n">
-        <v>1.64</v>
+        <v>13.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13749,13 +13749,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14701,13 +14701,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.28</v>
+        <v>3.6</v>
       </c>
       <c r="M122" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>13.2</v>
+        <v>1.9</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15177,13 +15177,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.11</v>
+        <v>3.36</v>
       </c>
       <c r="M125" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="N125" t="n">
-        <v>3.36</v>
+        <v>2.06</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>2.83</v>
+        <v>1.62</v>
       </c>
       <c r="M127" t="n">
-        <v>3.24</v>
+        <v>3.82</v>
       </c>
       <c r="N127" t="n">
-        <v>2.44</v>
+        <v>5.19</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="M128" t="n">
-        <v>3.1</v>
+        <v>3.83</v>
       </c>
       <c r="N128" t="n">
-        <v>2.5</v>
+        <v>4.58</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="M129" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N129" t="n">
-        <v>5.75</v>
+        <v>3.11</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AB129" t="n">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="M130" t="n">
-        <v>3.29</v>
+        <v>4.1</v>
       </c>
       <c r="N130" t="n">
-        <v>3.12</v>
+        <v>4.78</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.69</v>
+        <v>5.67</v>
       </c>
       <c r="M131" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="N131" t="n">
-        <v>2.57</v>
+        <v>1.56</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16058,7 +16058,7 @@
         <v>2</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>5.67</v>
+        <v>2.55</v>
       </c>
       <c r="M132" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>1.56</v>
+        <v>2.55</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="M134" t="n">
-        <v>3.62</v>
+        <v>3.81</v>
       </c>
       <c r="N134" t="n">
-        <v>4.04</v>
+        <v>4.63</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>4.23</v>
+        <v>2.22</v>
       </c>
       <c r="M135" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="N135" t="n">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,7 +16531,7 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB135" t="n">
         <v>1.93</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.19</v>
+        <v>2.69</v>
       </c>
       <c r="M136" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N136" t="n">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16653,7 +16653,7 @@
         <v>2</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.41</v>
+        <v>3.42</v>
       </c>
       <c r="M137" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="N137" t="n">
-        <v>6.88</v>
+        <v>1.93</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="AB137" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="M138" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N138" t="n">
-        <v>3.11</v>
+        <v>2.5</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.11</v>
+        <v>4.23</v>
       </c>
       <c r="M139" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
       <c r="N139" t="n">
-        <v>3.24</v>
+        <v>1.79</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>2.22</v>
+        <v>1.55</v>
       </c>
       <c r="M140" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="N140" t="n">
-        <v>3.05</v>
+        <v>5.75</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB140" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.62</v>
+        <v>2.83</v>
       </c>
       <c r="M141" t="n">
-        <v>3.82</v>
+        <v>3.24</v>
       </c>
       <c r="N141" t="n">
-        <v>5.19</v>
+        <v>2.44</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>3.05</v>
+        <v>1.41</v>
       </c>
       <c r="M142" t="n">
-        <v>3.04</v>
+        <v>4.7</v>
       </c>
       <c r="N142" t="n">
-        <v>2.43</v>
+        <v>6.88</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB142" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="M143" t="n">
-        <v>3.41</v>
+        <v>3.04</v>
       </c>
       <c r="N143" t="n">
-        <v>2.06</v>
+        <v>2.43</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>3.82</v>
+        <v>2.11</v>
       </c>
       <c r="M144" t="n">
-        <v>3.42</v>
+        <v>3.39</v>
       </c>
       <c r="N144" t="n">
-        <v>1.91</v>
+        <v>3.36</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17605,7 +17605,7 @@
         <v>1.98</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.7</v>
+        <v>2.29</v>
       </c>
       <c r="M145" t="n">
-        <v>3.81</v>
+        <v>3.29</v>
       </c>
       <c r="N145" t="n">
-        <v>4.63</v>
+        <v>3.12</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.55</v>
+        <v>2.11</v>
       </c>
       <c r="M146" t="n">
-        <v>3.25</v>
+        <v>3.58</v>
       </c>
       <c r="N146" t="n">
-        <v>2.55</v>
+        <v>3.24</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.63</v>
+        <v>2.19</v>
       </c>
       <c r="M147" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N147" t="n">
-        <v>4.78</v>
+        <v>3.25</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>1.69</v>
+        <v>3.82</v>
       </c>
       <c r="M148" t="n">
-        <v>3.83</v>
+        <v>3.42</v>
       </c>
       <c r="N148" t="n">
-        <v>4.58</v>
+        <v>1.91</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>3.42</v>
+        <v>1.82</v>
       </c>
       <c r="M149" t="n">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="N149" t="n">
-        <v>1.93</v>
+        <v>4.04</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M152" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18560,10 +18560,10 @@
         <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD152" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18747,13 +18747,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18862,17 +18862,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="M155" t="n">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="N155" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,16 +18911,16 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AD155" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.81</v>
+        <v>1.21</v>
       </c>
       <c r="M157" t="n">
-        <v>3.42</v>
+        <v>5.65</v>
       </c>
       <c r="N157" t="n">
-        <v>1.93</v>
+        <v>14.7</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19219,17 +19219,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.21</v>
+        <v>3.38</v>
       </c>
       <c r="M158" t="n">
-        <v>5</v>
+        <v>2.98</v>
       </c>
       <c r="N158" t="n">
-        <v>6.5</v>
+        <v>2.33</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19268,16 +19268,16 @@
         <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1.21</v>
+        <v>3.28</v>
       </c>
       <c r="M160" t="n">
-        <v>5.65</v>
+        <v>3.14</v>
       </c>
       <c r="N160" t="n">
-        <v>14.7</v>
+        <v>2.46</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="M166" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="N166" t="n">
-        <v>4.84</v>
+        <v>3.66</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="M167" t="n">
-        <v>3.76</v>
+        <v>4.55</v>
       </c>
       <c r="N167" t="n">
-        <v>4.37</v>
+        <v>6.05</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20339,10 +20339,10 @@
         <v>0</v>
       </c>
       <c r="AA167" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC167" t="n">
         <v>0</v>
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M170" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N171" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="M174" t="n">
-        <v>4.55</v>
+        <v>3.78</v>
       </c>
       <c r="N174" t="n">
-        <v>6.05</v>
+        <v>4.84</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB174" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>4.26</v>
+        <v>1.72</v>
       </c>
       <c r="M185" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N185" t="n">
-        <v>1.7</v>
+        <v>4.48</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22600,10 +22600,10 @@
         <v>0</v>
       </c>
       <c r="AA186" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB186" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="M187" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="N187" t="n">
-        <v>2.4</v>
+        <v>3.22</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M189" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.13</v>
+        <v>4.8</v>
       </c>
       <c r="M194" t="n">
-        <v>3.48</v>
+        <v>3.56</v>
       </c>
       <c r="N194" t="n">
-        <v>3.22</v>
+        <v>1.9</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>2.68</v>
+        <v>3.01</v>
       </c>
       <c r="M196" t="n">
-        <v>3.17</v>
+        <v>3.84</v>
       </c>
       <c r="N196" t="n">
-        <v>2.83</v>
+        <v>2.37</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB199" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M201" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.68</v>
+        <v>2.06</v>
       </c>
       <c r="M203" t="n">
-        <v>3.14</v>
+        <v>3.54</v>
       </c>
       <c r="N203" t="n">
-        <v>2.63</v>
+        <v>3.81</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.15</v>
+        <v>2.68</v>
       </c>
       <c r="M206" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="N206" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>3.39</v>
+        <v>1.77</v>
       </c>
       <c r="M209" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N209" t="n">
-        <v>1.95</v>
+        <v>3.97</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.3</v>
+        <v>3.39</v>
       </c>
       <c r="M211" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="N211" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M212" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="N212" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>2.57</v>
+        <v>1.64</v>
       </c>
       <c r="M214" t="n">
-        <v>3.34</v>
+        <v>3.68</v>
       </c>
       <c r="N214" t="n">
-        <v>2.38</v>
+        <v>4.62</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB214" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.64</v>
+        <v>2.57</v>
       </c>
       <c r="M217" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="N217" t="n">
-        <v>4.62</v>
+        <v>2.38</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB217" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="M221" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="N221" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="M222" t="n">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="N222" t="n">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27003,10 +27003,10 @@
         <v>0</v>
       </c>
       <c r="AA223" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.77</v>
+        <v>2.2</v>
       </c>
       <c r="M224" t="n">
-        <v>3.44</v>
+        <v>3.58</v>
       </c>
       <c r="N224" t="n">
-        <v>2.56</v>
+        <v>3.24</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB224" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2527,22 +2527,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,17 +3035,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,23 +3991,23 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O30" t="n">
+        <v>6</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.83</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="N30" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,10 +4155,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
-        <v>3.38</v>
+        <v>3.84</v>
       </c>
       <c r="N37" t="n">
-        <v>3.36</v>
+        <v>4.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.04</v>
+        <v>2.45</v>
       </c>
       <c r="M38" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>3.56</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.45</v>
+        <v>2.04</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>3.56</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.65</v>
+        <v>2.11</v>
       </c>
       <c r="M43" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="N43" t="n">
-        <v>2.06</v>
+        <v>3.36</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.29</v>
+        <v>6.43</v>
       </c>
       <c r="M45" t="n">
-        <v>3.28</v>
+        <v>4.09</v>
       </c>
       <c r="N45" t="n">
-        <v>2.18</v>
+        <v>1.41</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -5940,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.9</v>
+        <v>3.43</v>
       </c>
       <c r="M48" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="N48" t="n">
-        <v>4.38</v>
+        <v>2.07</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="M72" t="n">
-        <v>3.13</v>
+        <v>3.46</v>
       </c>
       <c r="N72" t="n">
-        <v>3.66</v>
+        <v>4.43</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="M73" t="n">
-        <v>2.8</v>
+        <v>3.04</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>3.47</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9191,7 +9191,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9584,13 +9584,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -9629,10 +9629,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="M79" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="N79" t="n">
-        <v>4.43</v>
+        <v>3.53</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10224,10 +10224,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>3.23</v>
+        <v>1.83</v>
       </c>
       <c r="M83" t="n">
-        <v>3.56</v>
+        <v>4.12</v>
       </c>
       <c r="N83" t="n">
-        <v>2.36</v>
+        <v>4.42</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>4.22</v>
+        <v>3.23</v>
       </c>
       <c r="M84" t="n">
-        <v>4.27</v>
+        <v>3.56</v>
       </c>
       <c r="N84" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB84" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.85</v>
+        <v>5.69</v>
       </c>
       <c r="M91" t="n">
-        <v>3.2</v>
+        <v>4.37</v>
       </c>
       <c r="N91" t="n">
-        <v>4.5</v>
+        <v>1.64</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,22 +11452,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12604,10 +12604,10 @@
         <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13273,13 +13273,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -13318,10 +13318,10 @@
         <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.28</v>
+        <v>5.52</v>
       </c>
       <c r="M111" t="n">
-        <v>6.3</v>
+        <v>3.92</v>
       </c>
       <c r="N111" t="n">
-        <v>13.2</v>
+        <v>1.57</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AB111" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.98</v>
+        <v>2.92</v>
       </c>
       <c r="M114" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>3.77</v>
+        <v>2.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14032,10 +14032,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="M118" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
       <c r="N118" t="n">
-        <v>4.5</v>
+        <v>13.2</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14582,13 +14582,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>3.36</v>
+        <v>2.29</v>
       </c>
       <c r="M125" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="N125" t="n">
-        <v>2.06</v>
+        <v>3.11</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M126" t="n">
-        <v>3.64</v>
+        <v>3.82</v>
       </c>
       <c r="N126" t="n">
-        <v>5.22</v>
+        <v>5.19</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M127" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="N127" t="n">
-        <v>5.19</v>
+        <v>4.78</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15579,10 +15579,10 @@
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>1.69</v>
+        <v>3.05</v>
       </c>
       <c r="M128" t="n">
-        <v>3.83</v>
+        <v>3.04</v>
       </c>
       <c r="N128" t="n">
-        <v>4.58</v>
+        <v>2.43</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="M129" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="N129" t="n">
-        <v>3.11</v>
+        <v>3.36</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="M130" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N130" t="n">
-        <v>4.78</v>
+        <v>5.75</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB130" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>5.67</v>
+        <v>2.7</v>
       </c>
       <c r="M131" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="N131" t="n">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="N132" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="M133" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="N133" t="n">
-        <v>3.48</v>
+        <v>2.44</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,55 +16367,55 @@
         </is>
       </c>
       <c r="L134" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M134" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N134" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB134" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M134" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N134" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>2</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.22</v>
+        <v>1.69</v>
       </c>
       <c r="M135" t="n">
-        <v>3.46</v>
+        <v>3.83</v>
       </c>
       <c r="N135" t="n">
-        <v>3.05</v>
+        <v>4.58</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M136" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="N136" t="n">
-        <v>2.57</v>
+        <v>6.88</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AB136" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>3.42</v>
+        <v>2.29</v>
       </c>
       <c r="M137" t="n">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="N137" t="n">
-        <v>1.93</v>
+        <v>3.12</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2.7</v>
+        <v>4.23</v>
       </c>
       <c r="M138" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N138" t="n">
-        <v>2.5</v>
+        <v>1.79</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB138" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>4.23</v>
+        <v>2.03</v>
       </c>
       <c r="M139" t="n">
-        <v>3.65</v>
+        <v>3.48</v>
       </c>
       <c r="N139" t="n">
-        <v>1.79</v>
+        <v>3.48</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="M140" t="n">
-        <v>3.7</v>
+        <v>3.42</v>
       </c>
       <c r="N140" t="n">
-        <v>5.75</v>
+        <v>1.91</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB140" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="M141" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="N141" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB141" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.41</v>
+        <v>5.67</v>
       </c>
       <c r="M142" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="N142" t="n">
-        <v>6.88</v>
+        <v>1.56</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>3.05</v>
+        <v>2.55</v>
       </c>
       <c r="M143" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="N143" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17521,7 +17521,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="M144" t="n">
-        <v>3.39</v>
+        <v>3.64</v>
       </c>
       <c r="N144" t="n">
-        <v>3.36</v>
+        <v>5.22</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="M145" t="n">
-        <v>3.29</v>
+        <v>3.81</v>
       </c>
       <c r="N145" t="n">
-        <v>3.12</v>
+        <v>4.63</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>2.11</v>
+        <v>3.36</v>
       </c>
       <c r="M146" t="n">
-        <v>3.58</v>
+        <v>3.41</v>
       </c>
       <c r="N146" t="n">
-        <v>3.24</v>
+        <v>2.06</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB146" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="M147" t="n">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="N147" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="M148" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="N148" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18509,13 +18509,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>5.23</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>7.75</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -18560,10 +18560,10 @@
         <v>0</v>
       </c>
       <c r="AC152" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD152" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE152" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18743,17 +18743,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,16 +18792,16 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC154" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18862,17 +18862,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.21</v>
+        <v>3.28</v>
       </c>
       <c r="M155" t="n">
-        <v>5</v>
+        <v>3.14</v>
       </c>
       <c r="N155" t="n">
-        <v>6.5</v>
+        <v>2.46</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18911,16 +18911,16 @@
         <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD155" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.21</v>
+        <v>3.81</v>
       </c>
       <c r="M157" t="n">
-        <v>5.65</v>
+        <v>3.42</v>
       </c>
       <c r="N157" t="n">
-        <v>14.7</v>
+        <v>1.93</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19149,10 +19149,10 @@
         <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC157" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19393,10 +19393,10 @@
         <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD159" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N160" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -19792,12 +19792,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="M166" t="n">
-        <v>3.14</v>
+        <v>3.78</v>
       </c>
       <c r="N166" t="n">
-        <v>3.66</v>
+        <v>4.84</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="M170" t="n">
-        <v>3.76</v>
+        <v>4.55</v>
       </c>
       <c r="N170" t="n">
-        <v>4.37</v>
+        <v>6.05</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20696,10 +20696,10 @@
         <v>0</v>
       </c>
       <c r="AA170" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB170" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="M172" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="N172" t="n">
-        <v>4.62</v>
+        <v>4.37</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="M174" t="n">
-        <v>3.78</v>
+        <v>3.14</v>
       </c>
       <c r="N174" t="n">
-        <v>4.84</v>
+        <v>3.66</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21172,10 +21172,10 @@
         <v>0</v>
       </c>
       <c r="AA174" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB174" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC174" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>1.72</v>
+        <v>4.26</v>
       </c>
       <c r="M185" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N185" t="n">
-        <v>4.48</v>
+        <v>1.7</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4.26</v>
+        <v>4.8</v>
       </c>
       <c r="M189" t="n">
-        <v>4.1</v>
+        <v>3.56</v>
       </c>
       <c r="N189" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB189" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB198" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24147,10 +24147,10 @@
         <v>0</v>
       </c>
       <c r="AA199" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB199" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="M203" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N203" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="M204" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N204" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24861,10 +24861,10 @@
         <v>0</v>
       </c>
       <c r="AA205" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB205" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.68</v>
+        <v>2.05</v>
       </c>
       <c r="M206" t="n">
-        <v>3.14</v>
+        <v>3.68</v>
       </c>
       <c r="N206" t="n">
-        <v>2.63</v>
+        <v>3.9</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="M208" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="N208" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M209" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="N209" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25337,10 +25337,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB209" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>2.42</v>
+        <v>1.77</v>
       </c>
       <c r="M210" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N210" t="n">
-        <v>2.91</v>
+        <v>3.97</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB210" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.39</v>
+        <v>2.42</v>
       </c>
       <c r="M211" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N211" t="n">
-        <v>1.95</v>
+        <v>2.91</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.3</v>
+        <v>3.39</v>
       </c>
       <c r="M212" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="N212" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="M214" t="n">
-        <v>3.68</v>
+        <v>3.96</v>
       </c>
       <c r="N214" t="n">
-        <v>4.62</v>
+        <v>5.16</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M215" t="n">
-        <v>3.96</v>
+        <v>3.68</v>
       </c>
       <c r="N215" t="n">
-        <v>5.16</v>
+        <v>4.62</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="M219" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N219" t="n">
-        <v>2.38</v>
+        <v>4.32</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB219" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="M220" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="N220" t="n">
-        <v>4.32</v>
+        <v>2.38</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB220" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="M221" t="n">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="N221" t="n">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="M222" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="N222" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -28231,7 +28231,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -28263,7 +28263,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Felgueiras 1932</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Felgueiras 1932</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="N22" t="n">
-        <v>4.31</v>
+        <v>3.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,26 +3392,26 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="M37" t="n">
-        <v>3.84</v>
+        <v>3.36</v>
       </c>
       <c r="N37" t="n">
-        <v>4.74</v>
+        <v>3.56</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4907,7 +4907,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.45</v>
+        <v>2.11</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N38" t="n">
-        <v>2.6</v>
+        <v>3.36</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3.65</v>
+        <v>1.68</v>
       </c>
       <c r="M40" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="N40" t="n">
-        <v>2.06</v>
+        <v>4.74</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>3.65</v>
       </c>
       <c r="M41" t="n">
-        <v>3.36</v>
+        <v>3.24</v>
       </c>
       <c r="N41" t="n">
-        <v>3.56</v>
+        <v>2.06</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5464,10 +5464,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="M43" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>3.36</v>
+        <v>2.6</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5776,13 +5776,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5821,10 +5821,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6609,13 +6609,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8715,7 +8715,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="M74" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="N74" t="n">
-        <v>2.1</v>
+        <v>4.89</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB74" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9310,7 +9310,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB78" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>3.23</v>
+        <v>2.14</v>
       </c>
       <c r="M84" t="n">
-        <v>3.56</v>
+        <v>3.66</v>
       </c>
       <c r="N84" t="n">
-        <v>2.36</v>
+        <v>3.64</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>4.22</v>
+        <v>3.88</v>
       </c>
       <c r="M85" t="n">
-        <v>4.27</v>
+        <v>3.64</v>
       </c>
       <c r="N85" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AB85" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="M86" t="n">
-        <v>3.64</v>
+        <v>4.27</v>
       </c>
       <c r="N86" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.14</v>
+        <v>3.23</v>
       </c>
       <c r="M88" t="n">
-        <v>3.66</v>
+        <v>3.56</v>
       </c>
       <c r="N88" t="n">
-        <v>3.64</v>
+        <v>2.36</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11250,13 +11250,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -11295,10 +11295,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11369,13 +11369,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11928,22 +11928,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12523,7 +12523,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13237,7 +13237,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13630,13 +13630,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         <v>0</v>
       </c>
       <c r="AA111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC111" t="n">
         <v>0</v>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.92</v>
+        <v>1.85</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N114" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14344,13 +14344,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -14389,10 +14389,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14508,10 +14508,10 @@
         <v>0</v>
       </c>
       <c r="AA118" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.13</v>
+        <v>1.28</v>
       </c>
       <c r="M121" t="n">
-        <v>3.5</v>
+        <v>6.3</v>
       </c>
       <c r="N121" t="n">
-        <v>3.84</v>
+        <v>13.2</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB121" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>1.61</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15103,10 +15103,10 @@
         <v>0</v>
       </c>
       <c r="AA123" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB123" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15299,10 +15299,10 @@
         <v>2.29</v>
       </c>
       <c r="M125" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="N125" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AB125" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M126" t="n">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="N126" t="n">
-        <v>5.19</v>
+        <v>5.22</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15460,10 +15460,10 @@
         <v>0</v>
       </c>
       <c r="AA126" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="M127" t="n">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="N127" t="n">
-        <v>4.78</v>
+        <v>4.58</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15617,7 +15617,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.05</v>
+        <v>2.11</v>
       </c>
       <c r="M128" t="n">
-        <v>3.04</v>
+        <v>3.58</v>
       </c>
       <c r="N128" t="n">
-        <v>2.43</v>
+        <v>3.24</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>2.11</v>
+        <v>3.05</v>
       </c>
       <c r="M129" t="n">
-        <v>3.39</v>
+        <v>3.04</v>
       </c>
       <c r="N129" t="n">
-        <v>3.36</v>
+        <v>2.43</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="M130" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="N130" t="n">
-        <v>5.75</v>
+        <v>4.04</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AB130" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.7</v>
+        <v>1.63</v>
       </c>
       <c r="M131" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="N131" t="n">
-        <v>2.5</v>
+        <v>4.78</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="M132" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="N132" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="M133" t="n">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="N133" t="n">
-        <v>2.44</v>
+        <v>3.48</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M135" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="N135" t="n">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB135" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="M136" t="n">
-        <v>4.7</v>
+        <v>3.1</v>
       </c>
       <c r="N136" t="n">
-        <v>6.88</v>
+        <v>2.5</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB136" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="M137" t="n">
-        <v>3.29</v>
+        <v>3.82</v>
       </c>
       <c r="N137" t="n">
-        <v>3.12</v>
+        <v>5.19</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB137" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.03</v>
+        <v>2.55</v>
       </c>
       <c r="M139" t="n">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>3.48</v>
+        <v>2.55</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB139" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,55 +17081,55 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.82</v>
+        <v>3.36</v>
       </c>
       <c r="M140" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="N140" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB140" t="n">
         <v>1.91</v>
-      </c>
-      <c r="O140" t="n">
-        <v>0</v>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
-      <c r="R140" t="n">
-        <v>0</v>
-      </c>
-      <c r="S140" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" t="n">
-        <v>0</v>
-      </c>
-      <c r="U140" t="n">
-        <v>0</v>
-      </c>
-      <c r="V140" t="n">
-        <v>0</v>
-      </c>
-      <c r="W140" t="n">
-        <v>0</v>
-      </c>
-      <c r="X140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y140" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z140" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA140" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>1.78</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>2.69</v>
+        <v>1.41</v>
       </c>
       <c r="M141" t="n">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="N141" t="n">
-        <v>2.57</v>
+        <v>6.88</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AB141" t="n">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>5.67</v>
+        <v>1.55</v>
       </c>
       <c r="M142" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N142" t="n">
-        <v>1.56</v>
+        <v>5.75</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB142" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="M143" t="n">
-        <v>3.25</v>
+        <v>3.46</v>
       </c>
       <c r="N143" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1.63</v>
+        <v>3.82</v>
       </c>
       <c r="M144" t="n">
-        <v>3.64</v>
+        <v>3.42</v>
       </c>
       <c r="N144" t="n">
-        <v>5.22</v>
+        <v>1.91</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB144" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.7</v>
+        <v>2.69</v>
       </c>
       <c r="M145" t="n">
-        <v>3.81</v>
+        <v>3.28</v>
       </c>
       <c r="N145" t="n">
-        <v>4.63</v>
+        <v>2.57</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AB145" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="M146" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N146" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17917,10 +17917,10 @@
         <v>2.11</v>
       </c>
       <c r="M147" t="n">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="N147" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB147" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>3.42</v>
+        <v>5.67</v>
       </c>
       <c r="M148" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="N148" t="n">
-        <v>1.93</v>
+        <v>1.56</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>1.82</v>
+        <v>2.83</v>
       </c>
       <c r="M149" t="n">
-        <v>3.62</v>
+        <v>3.24</v>
       </c>
       <c r="N149" t="n">
-        <v>4.04</v>
+        <v>2.44</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>1.21</v>
+        <v>3.38</v>
       </c>
       <c r="M153" t="n">
-        <v>5.65</v>
+        <v>2.98</v>
       </c>
       <c r="N153" t="n">
-        <v>14.7</v>
+        <v>2.33</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18743,17 +18743,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -18792,16 +18792,16 @@
         <v>0</v>
       </c>
       <c r="AA154" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB154" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC154" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD154" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE154" t="n">
         <v>0</v>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>3.28</v>
+        <v>1.21</v>
       </c>
       <c r="M155" t="n">
-        <v>3.14</v>
+        <v>5.65</v>
       </c>
       <c r="N155" t="n">
-        <v>2.46</v>
+        <v>14.7</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,61 +19104,61 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3.81</v>
+        <v>1.39</v>
       </c>
       <c r="M157" t="n">
-        <v>3.42</v>
+        <v>5.23</v>
       </c>
       <c r="N157" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0</v>
+      </c>
+      <c r="S157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
+        <v>0</v>
+      </c>
+      <c r="U157" t="n">
+        <v>0</v>
+      </c>
+      <c r="V157" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" t="n">
+        <v>0</v>
+      </c>
+      <c r="X157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC157" t="n">
         <v>1.93</v>
       </c>
-      <c r="O157" t="n">
-        <v>0</v>
-      </c>
-      <c r="P157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" t="n">
-        <v>0</v>
-      </c>
-      <c r="W157" t="n">
-        <v>0</v>
-      </c>
-      <c r="X157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="n">
+      <c r="AD157" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N158" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="M159" t="n">
-        <v>5.23</v>
+        <v>5</v>
       </c>
       <c r="N159" t="n">
-        <v>7.75</v>
+        <v>6.5</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB159" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC159" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB162" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N166" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB166" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M171" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB171" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20889,13 +20889,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N172" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AA172" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB172" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC172" t="n">
         <v>0</v>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M173" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N173" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="M174" t="n">
-        <v>3.14</v>
+        <v>4.12</v>
       </c>
       <c r="N174" t="n">
-        <v>3.66</v>
+        <v>4.62</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M176" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N176" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB177" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21718,7 +21718,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,7 +21956,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L181" t="n">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>4.26</v>
+        <v>2.13</v>
       </c>
       <c r="M185" t="n">
-        <v>4.1</v>
+        <v>3.48</v>
       </c>
       <c r="N185" t="n">
-        <v>1.7</v>
+        <v>3.22</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.13</v>
+        <v>2.75</v>
       </c>
       <c r="M187" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="N187" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N188" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22912,13 +22912,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -22957,10 +22957,10 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB189" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC189" t="n">
         <v>0</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N190" t="n">
-        <v>4.48</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB191" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="N197" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>3.01</v>
+        <v>1.78</v>
       </c>
       <c r="M198" t="n">
-        <v>3.84</v>
+        <v>4.04</v>
       </c>
       <c r="N198" t="n">
-        <v>2.37</v>
+        <v>4.88</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AB198" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24340,13 +24340,13 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N201" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="M203" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="N203" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB203" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.6</v>
+        <v>2.15</v>
       </c>
       <c r="M204" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N204" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="N205" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M206" t="n">
-        <v>3.68</v>
+        <v>3</v>
       </c>
       <c r="N206" t="n">
-        <v>3.9</v>
+        <v>2.67</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB206" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N207" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25385,12 +25385,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -25411,13 +25411,13 @@
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1.77</v>
+        <v>2.42</v>
       </c>
       <c r="M210" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N210" t="n">
-        <v>3.97</v>
+        <v>2.91</v>
       </c>
       <c r="O210" t="n">
         <v>0</v>
@@ -25456,10 +25456,10 @@
         <v>0</v>
       </c>
       <c r="AA210" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB210" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC210" t="n">
         <v>0</v>
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>2.42</v>
+        <v>3.39</v>
       </c>
       <c r="M211" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N211" t="n">
-        <v>2.91</v>
+        <v>1.95</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB211" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>3.39</v>
+        <v>1.77</v>
       </c>
       <c r="M212" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N212" t="n">
-        <v>1.95</v>
+        <v>3.97</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="M213" t="n">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="N213" t="n">
-        <v>4.17</v>
+        <v>2.38</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB213" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="M214" t="n">
-        <v>3.96</v>
+        <v>3.72</v>
       </c>
       <c r="N214" t="n">
-        <v>5.16</v>
+        <v>4.17</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="M217" t="n">
-        <v>3.34</v>
+        <v>3.96</v>
       </c>
       <c r="N217" t="n">
-        <v>2.38</v>
+        <v>5.16</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26289,10 +26289,10 @@
         <v>0</v>
       </c>
       <c r="AA217" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB217" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC217" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="M221" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="N221" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="M222" t="n">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="N222" t="n">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28144,7 +28144,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2646,22 +2646,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tampines Rovers</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3042,10 +3042,10 @@
         <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="N22" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3161,10 +3161,10 @@
         <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="N23" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="M38" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="N38" t="n">
-        <v>3.36</v>
+        <v>3.56</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="N39" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.68</v>
+        <v>3.65</v>
       </c>
       <c r="M40" t="n">
-        <v>3.84</v>
+        <v>3.24</v>
       </c>
       <c r="N40" t="n">
-        <v>4.74</v>
+        <v>2.06</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,13 +5300,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.65</v>
+        <v>1.68</v>
       </c>
       <c r="M41" t="n">
-        <v>3.24</v>
+        <v>3.84</v>
       </c>
       <c r="N41" t="n">
-        <v>2.06</v>
+        <v>4.74</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5345,10 +5345,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5419,13 +5419,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5583,10 +5583,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>6.43</v>
+        <v>3.29</v>
       </c>
       <c r="M44" t="n">
-        <v>4.09</v>
+        <v>3.28</v>
       </c>
       <c r="N44" t="n">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -5702,10 +5702,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.43</v>
+        <v>1.79</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>3.72</v>
       </c>
       <c r="N47" t="n">
-        <v>2.07</v>
+        <v>4.68</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6966,13 +6966,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.38</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7882,7 +7882,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N70" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AB70" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -8989,13 +8989,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9034,10 +9034,10 @@
         <v>0</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB72" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
         <v>0</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9201,12 +9201,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9227,13 +9227,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.93</v>
+        <v>2.11</v>
       </c>
       <c r="M74" t="n">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N74" t="n">
-        <v>4.89</v>
+        <v>3.66</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9272,10 +9272,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -9320,12 +9320,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -9346,13 +9346,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="M75" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N75" t="n">
-        <v>3.47</v>
+        <v>4.89</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -9391,10 +9391,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -9465,13 +9465,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -9510,10 +9510,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -9558,12 +9558,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -9703,13 +9703,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -9748,10 +9748,10 @@
         <v>0</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
@@ -9796,12 +9796,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sigma Olomouc</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10153,12 +10153,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Sigma Olomouc</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10179,13 +10179,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -10298,13 +10298,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.42</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -10343,10 +10343,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -10391,12 +10391,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mainz 05</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -10417,13 +10417,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.14</v>
+        <v>4.22</v>
       </c>
       <c r="M84" t="n">
-        <v>3.66</v>
+        <v>4.27</v>
       </c>
       <c r="N84" t="n">
-        <v>3.64</v>
+        <v>1.84</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -10462,10 +10462,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -10510,12 +10510,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -10536,13 +10536,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.88</v>
+        <v>1.83</v>
       </c>
       <c r="M85" t="n">
-        <v>3.64</v>
+        <v>4.12</v>
       </c>
       <c r="N85" t="n">
-        <v>2.07</v>
+        <v>4.42</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -10581,10 +10581,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -10655,13 +10655,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>4.22</v>
+        <v>3.23</v>
       </c>
       <c r="M86" t="n">
-        <v>4.27</v>
+        <v>3.56</v>
       </c>
       <c r="N86" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -10700,10 +10700,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB86" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Mainz 05</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -10774,13 +10774,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -10819,10 +10819,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -10867,12 +10867,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -10893,13 +10893,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="M88" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="N88" t="n">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -10938,10 +10938,10 @@
         <v>0</v>
       </c>
       <c r="AA88" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vasco da Gama Vidigueira</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>FC Serpa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Moncarapachense</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>5.69</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -11533,10 +11533,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -11571,7 +11571,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lagoa</t>
+          <t>Anadia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Comércio Indústria</t>
+          <t>Aparecida</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Vitória de Sernache</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Benfica Castelo Branco</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="M96" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="N96" t="n">
-        <v>3.43</v>
+        <v>2.87</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>O Elvas</t>
+          <t>União Santarém</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sintrense</t>
+          <t>CD Mafra</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -11964,13 +11964,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -12083,13 +12083,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -12128,10 +12128,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Vila Meã</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Salgueiros</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -12202,13 +12202,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>5.69</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -12321,13 +12321,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="M100" t="n">
-        <v>3.63</v>
+        <v>6.3</v>
       </c>
       <c r="N100" t="n">
-        <v>3.77</v>
+        <v>13.2</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -12366,10 +12366,10 @@
         <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Juventude Évora</t>
+          <t>Varzim</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -12440,13 +12440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -12533,12 +12533,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>União Santarém</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>CD Mafra</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -12559,13 +12559,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.59</v>
+        <v>1.79</v>
       </c>
       <c r="M103" t="n">
-        <v>3.86</v>
+        <v>3.4</v>
       </c>
       <c r="N103" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>SC Beira-Mar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Resende</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -12999,22 +12999,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -13128,12 +13128,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Vitória de Sernache</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Benfica Castelo Branco</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -13154,13 +13154,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -13199,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -13247,12 +13247,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Anadia</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Aparecida</t>
+          <t>Florgrade</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -13475,22 +13475,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vilaverdense</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Monção</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Lagoa</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Comércio Indústria</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>Vasco da Gama Vidigueira</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -13832,7 +13832,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -13842,12 +13842,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -13868,13 +13868,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -13961,12 +13961,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Varzim</t>
+          <t>O Elvas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Sintrense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -13987,13 +13987,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -14080,12 +14080,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -14106,55 +14106,55 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.6</v>
+        <v>5.52</v>
       </c>
       <c r="M115" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="N115" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>0</v>
+      </c>
+      <c r="U115" t="n">
+        <v>0</v>
+      </c>
+      <c r="V115" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" t="n">
         <v>1.9</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>0</v>
-      </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC115" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Vila Meã</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Salgueiros</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -14556,12 +14556,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SC Beira-Mar</t>
+          <t>Juventude Évora</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Resende</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -14675,12 +14675,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Vilaverdense</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Florgrade</t>
+          <t>Monção</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -14794,12 +14794,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FC Serpa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Moncarapachense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -14820,13 +14820,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>13.2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -14865,10 +14865,10 @@
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB121" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
         <v>0</v>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -14913,12 +14913,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -14939,13 +14939,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>5.52</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -14984,10 +14984,10 @@
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC122" t="n">
         <v>0</v>
@@ -15022,7 +15022,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -15032,12 +15032,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -15058,13 +15058,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -15141,7 +15141,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -15296,13 +15296,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="M125" t="n">
-        <v>3.29</v>
+        <v>3.81</v>
       </c>
       <c r="N125" t="n">
-        <v>3.12</v>
+        <v>4.63</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -15341,10 +15341,10 @@
         <v>0</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
@@ -15379,7 +15379,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -15389,12 +15389,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -15415,13 +15415,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="M126" t="n">
-        <v>3.64</v>
+        <v>3.29</v>
       </c>
       <c r="N126" t="n">
-        <v>5.22</v>
+        <v>3.12</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -15508,12 +15508,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -15534,13 +15534,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.69</v>
+        <v>2.11</v>
       </c>
       <c r="M127" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="N127" t="n">
-        <v>4.58</v>
+        <v>3.24</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -15627,12 +15627,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -15653,13 +15653,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="M128" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="N128" t="n">
-        <v>3.24</v>
+        <v>3.05</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -15698,10 +15698,10 @@
         <v>0</v>
       </c>
       <c r="AA128" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC128" t="n">
         <v>0</v>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -15746,12 +15746,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -15772,13 +15772,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.05</v>
+        <v>1.82</v>
       </c>
       <c r="M129" t="n">
-        <v>3.04</v>
+        <v>3.62</v>
       </c>
       <c r="N129" t="n">
-        <v>2.43</v>
+        <v>4.04</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -15817,10 +15817,10 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.82</v>
+        <v>3.36</v>
       </c>
       <c r="M130" t="n">
-        <v>3.62</v>
+        <v>3.41</v>
       </c>
       <c r="N130" t="n">
-        <v>4.04</v>
+        <v>2.06</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -15984,12 +15984,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -16010,13 +16010,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.63</v>
+        <v>1.41</v>
       </c>
       <c r="M131" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="N131" t="n">
-        <v>4.78</v>
+        <v>6.88</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -16055,10 +16055,10 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -16129,13 +16129,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>2.29</v>
+        <v>1.55</v>
       </c>
       <c r="M132" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N132" t="n">
-        <v>3.11</v>
+        <v>5.75</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -16174,10 +16174,10 @@
         <v>0</v>
       </c>
       <c r="AA132" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AB132" t="n">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -16222,12 +16222,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -16248,13 +16248,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M133" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="N133" t="n">
-        <v>3.48</v>
+        <v>2.5</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -16293,10 +16293,10 @@
         <v>0</v>
       </c>
       <c r="AA133" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB133" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC133" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -16341,12 +16341,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -16367,13 +16367,13 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="M134" t="n">
-        <v>3.3</v>
+        <v>3.82</v>
       </c>
       <c r="N134" t="n">
-        <v>3.25</v>
+        <v>5.19</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
@@ -16412,10 +16412,10 @@
         <v>0</v>
       </c>
       <c r="AA134" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AB134" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC134" t="n">
         <v>0</v>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,55 +16486,55 @@
         </is>
       </c>
       <c r="L135" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="M135" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB135" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="N135" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>2</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -16579,12 +16579,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -16605,13 +16605,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="M136" t="n">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="N136" t="n">
-        <v>2.5</v>
+        <v>3.36</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -16650,10 +16650,10 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB136" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC136" t="n">
         <v>0</v>
@@ -16698,12 +16698,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -16724,13 +16724,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="M137" t="n">
-        <v>3.82</v>
+        <v>3.04</v>
       </c>
       <c r="N137" t="n">
-        <v>5.19</v>
+        <v>2.43</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -16769,10 +16769,10 @@
         <v>0</v>
       </c>
       <c r="AA137" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB137" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC137" t="n">
         <v>0</v>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -16843,13 +16843,13 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>4.23</v>
+        <v>2.55</v>
       </c>
       <c r="M138" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N138" t="n">
-        <v>1.79</v>
+        <v>2.55</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
@@ -16888,10 +16888,10 @@
         <v>0</v>
       </c>
       <c r="AA138" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB138" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC138" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -16936,12 +16936,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -16962,13 +16962,13 @@
         </is>
       </c>
       <c r="L139" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="M139" t="n">
         <v>3.25</v>
       </c>
       <c r="N139" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="O139" t="n">
         <v>0</v>
@@ -17007,10 +17007,10 @@
         <v>0</v>
       </c>
       <c r="AA139" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AB139" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC139" t="n">
         <v>0</v>
@@ -17055,12 +17055,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -17081,13 +17081,13 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>3.36</v>
+        <v>5.67</v>
       </c>
       <c r="M140" t="n">
-        <v>3.41</v>
+        <v>3.9</v>
       </c>
       <c r="N140" t="n">
-        <v>2.06</v>
+        <v>1.56</v>
       </c>
       <c r="O140" t="n">
         <v>0</v>
@@ -17126,10 +17126,10 @@
         <v>0</v>
       </c>
       <c r="AA140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB140" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>1.91</v>
       </c>
       <c r="AC140" t="n">
         <v>0</v>
@@ -17164,7 +17164,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -17174,12 +17174,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -17200,13 +17200,13 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>1.41</v>
+        <v>3.82</v>
       </c>
       <c r="M141" t="n">
-        <v>4.7</v>
+        <v>3.42</v>
       </c>
       <c r="N141" t="n">
-        <v>6.88</v>
+        <v>1.91</v>
       </c>
       <c r="O141" t="n">
         <v>0</v>
@@ -17245,10 +17245,10 @@
         <v>0</v>
       </c>
       <c r="AA141" t="n">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AB141" t="n">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="AC141" t="n">
         <v>0</v>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -17293,12 +17293,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -17319,13 +17319,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="M142" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N142" t="n">
-        <v>5.75</v>
+        <v>4.78</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -17364,10 +17364,10 @@
         <v>0</v>
       </c>
       <c r="AA142" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB142" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AC142" t="n">
         <v>0</v>
@@ -17402,7 +17402,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="M143" t="n">
-        <v>3.46</v>
+        <v>3.64</v>
       </c>
       <c r="N143" t="n">
-        <v>3.05</v>
+        <v>5.22</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB143" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>3.82</v>
+        <v>3.42</v>
       </c>
       <c r="M144" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="N144" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
       <c r="M145" t="n">
-        <v>3.28</v>
+        <v>3.83</v>
       </c>
       <c r="N145" t="n">
-        <v>2.57</v>
+        <v>4.58</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,55 +17795,55 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>3.42</v>
+        <v>4.23</v>
       </c>
       <c r="M146" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N146" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AB146" t="n">
         <v>1.93</v>
-      </c>
-      <c r="O146" t="n">
-        <v>0</v>
-      </c>
-      <c r="P146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0</v>
-      </c>
-      <c r="S146" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" t="n">
-        <v>0</v>
-      </c>
-      <c r="U146" t="n">
-        <v>0</v>
-      </c>
-      <c r="V146" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" t="n">
-        <v>0</v>
-      </c>
-      <c r="X146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y146" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z146" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB146" t="n">
-        <v>1.84</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -17888,12 +17888,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -17914,13 +17914,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="M147" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="N147" t="n">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -17959,10 +17959,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -17997,7 +17997,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>5.67</v>
+        <v>2.83</v>
       </c>
       <c r="M148" t="n">
-        <v>3.9</v>
+        <v>3.24</v>
       </c>
       <c r="N148" t="n">
-        <v>1.56</v>
+        <v>2.44</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB148" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="M149" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="N149" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -18245,12 +18245,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -18271,13 +18271,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -18364,12 +18364,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -18390,13 +18390,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N151" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="M153" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N153" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18830,7 +18830,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1.21</v>
+        <v>3.38</v>
       </c>
       <c r="M155" t="n">
-        <v>5.65</v>
+        <v>2.98</v>
       </c>
       <c r="N155" t="n">
-        <v>14.7</v>
+        <v>2.33</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="M157" t="n">
-        <v>5.23</v>
+        <v>5.65</v>
       </c>
       <c r="N157" t="n">
-        <v>7.75</v>
+        <v>14.7</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19155,10 +19155,10 @@
         <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19274,10 +19274,10 @@
         <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -19580,13 +19580,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M161" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -19625,10 +19625,10 @@
         <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC161" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -19699,13 +19699,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="N162" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -19744,10 +19744,10 @@
         <v>0</v>
       </c>
       <c r="AA162" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB162" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC162" t="n">
         <v>0</v>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="M170" t="n">
-        <v>4.55</v>
+        <v>4.12</v>
       </c>
       <c r="N170" t="n">
-        <v>6.05</v>
+        <v>4.62</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20853,7 +20853,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -20863,12 +20863,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -20972,7 +20972,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -20982,12 +20982,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -21008,13 +21008,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M173" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N173" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -21091,7 +21091,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21127,13 +21127,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N174" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21246,13 +21246,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -21329,7 +21329,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -21339,12 +21339,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Hajduk Split</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -21365,13 +21365,13 @@
         </is>
       </c>
       <c r="L176" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M176" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="O176" t="n">
         <v>0</v>
@@ -21410,10 +21410,10 @@
         <v>0</v>
       </c>
       <c r="AA176" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB176" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC176" t="n">
         <v>0</v>
@@ -21448,7 +21448,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -21458,12 +21458,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Hajduk Split</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -21484,13 +21484,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -21529,10 +21529,10 @@
         <v>0</v>
       </c>
       <c r="AA177" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB177" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC177" t="n">
         <v>0</v>
@@ -21567,7 +21567,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -21577,12 +21577,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21841,13 +21841,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -22043,7 +22043,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -22053,12 +22053,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22281,7 +22281,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -22291,12 +22291,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M185" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N185" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Wil</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="M186" t="n">
-        <v>3.7</v>
+        <v>3.48</v>
       </c>
       <c r="N186" t="n">
-        <v>4.48</v>
+        <v>3.22</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22674,13 +22674,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N188" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -23005,12 +23005,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Wil</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -23031,13 +23031,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M190" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>4.48</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23150,13 +23150,13 @@
         </is>
       </c>
       <c r="L191" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="N191" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
         <v>0</v>
@@ -23195,10 +23195,10 @@
         <v>0</v>
       </c>
       <c r="AA191" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB191" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC191" t="n">
         <v>0</v>
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N193" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N196" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB196" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB197" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1.78</v>
+        <v>2.68</v>
       </c>
       <c r="M198" t="n">
-        <v>4.04</v>
+        <v>3.17</v>
       </c>
       <c r="N198" t="n">
-        <v>4.88</v>
+        <v>2.83</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24028,10 +24028,10 @@
         <v>0</v>
       </c>
       <c r="AA198" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB198" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC198" t="n">
         <v>0</v>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -24102,13 +24102,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -24185,7 +24185,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -24195,12 +24195,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -24221,13 +24221,13 @@
         </is>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M200" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="N200" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="O200" t="n">
         <v>0</v>
@@ -24266,10 +24266,10 @@
         <v>0</v>
       </c>
       <c r="AA200" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB200" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC200" t="n">
         <v>0</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="M203" t="n">
-        <v>3.68</v>
+        <v>3.54</v>
       </c>
       <c r="N203" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24623,10 +24623,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N204" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="M205" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="N205" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -24899,7 +24899,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -24909,12 +24909,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -24935,13 +24935,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M206" t="n">
-        <v>3</v>
+        <v>3.68</v>
       </c>
       <c r="N206" t="n">
-        <v>2.67</v>
+        <v>3.9</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -24980,10 +24980,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -25018,7 +25018,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -25028,12 +25028,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -25054,13 +25054,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -25266,12 +25266,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -25292,13 +25292,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="M209" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="N209" t="n">
-        <v>3.7</v>
+        <v>3.97</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -25337,10 +25337,10 @@
         <v>0</v>
       </c>
       <c r="AA209" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB209" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC209" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="M212" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="N212" t="n">
-        <v>3.97</v>
+        <v>3.7</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB212" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -25732,7 +25732,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -25742,12 +25742,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -25768,13 +25768,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>2.57</v>
+        <v>1.82</v>
       </c>
       <c r="M213" t="n">
-        <v>3.34</v>
+        <v>3.79</v>
       </c>
       <c r="N213" t="n">
-        <v>2.38</v>
+        <v>4.37</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -25813,10 +25813,10 @@
         <v>0</v>
       </c>
       <c r="AA213" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB213" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC213" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -25861,12 +25861,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -25887,13 +25887,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="M214" t="n">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="N214" t="n">
-        <v>4.17</v>
+        <v>2.38</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -25932,10 +25932,10 @@
         <v>0</v>
       </c>
       <c r="AA214" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB214" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC214" t="n">
         <v>0</v>
@@ -25970,7 +25970,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -25980,12 +25980,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -26006,13 +26006,13 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="M215" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="N215" t="n">
-        <v>4.62</v>
+        <v>4.17</v>
       </c>
       <c r="O215" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="M216" t="n">
-        <v>3.79</v>
+        <v>3.96</v>
       </c>
       <c r="N216" t="n">
-        <v>4.37</v>
+        <v>5.16</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M217" t="n">
-        <v>3.96</v>
+        <v>3.68</v>
       </c>
       <c r="N217" t="n">
-        <v>5.16</v>
+        <v>4.62</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26446,7 +26446,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -26456,12 +26456,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -26482,13 +26482,13 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>1.73</v>
+        <v>2.77</v>
       </c>
       <c r="M219" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="N219" t="n">
-        <v>4.32</v>
+        <v>2.38</v>
       </c>
       <c r="O219" t="n">
         <v>0</v>
@@ -26527,10 +26527,10 @@
         <v>0</v>
       </c>
       <c r="AA219" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC219" t="n">
         <v>0</v>
@@ -26565,7 +26565,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -26575,12 +26575,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -26601,13 +26601,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>2.77</v>
+        <v>1.73</v>
       </c>
       <c r="M220" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="N220" t="n">
-        <v>2.38</v>
+        <v>4.32</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -26646,10 +26646,10 @@
         <v>0</v>
       </c>
       <c r="AA220" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB220" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC220" t="n">
         <v>0</v>
@@ -26684,7 +26684,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -26694,12 +26694,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -26720,13 +26720,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="M221" t="n">
-        <v>3.69</v>
+        <v>3.46</v>
       </c>
       <c r="N221" t="n">
-        <v>3.85</v>
+        <v>3.66</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -26765,10 +26765,10 @@
         <v>0</v>
       </c>
       <c r="AA221" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="AB221" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC221" t="n">
         <v>0</v>
@@ -26803,7 +26803,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -26813,12 +26813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -26839,13 +26839,13 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>2.21</v>
+        <v>1.94</v>
       </c>
       <c r="M222" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="N222" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="O222" t="n">
         <v>0</v>
@@ -26884,10 +26884,10 @@
         <v>0</v>
       </c>
       <c r="AA222" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="AB222" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC222" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M225" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -28241,12 +28241,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G234" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -5621,7 +5621,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -5657,13 +5657,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6097,7 +6097,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6133,13 +6133,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6178,10 +6178,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6252,13 +6252,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6297,10 +6297,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6371,13 +6371,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.9</v>
+        <v>3.29</v>
       </c>
       <c r="M50" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="N50" t="n">
-        <v>4.38</v>
+        <v>2.18</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6454,7 +6454,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6490,13 +6490,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -6847,13 +6847,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6940,12 +6940,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7204,13 +7204,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7773,12 +7773,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8011,12 +8011,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Legia Warszawa</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8275,13 +8275,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.58</v>
+        <v>2.6</v>
       </c>
       <c r="M66" t="n">
         <v>3.58</v>
       </c>
       <c r="N66" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Legia Warszawa</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -8394,13 +8394,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.6</v>
+        <v>3.58</v>
       </c>
       <c r="M67" t="n">
         <v>3.58</v>
       </c>
       <c r="N67" t="n">
-        <v>2.24</v>
+        <v>1.95</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -8439,10 +8439,10 @@
         <v>0</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8487,12 +8487,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -8558,10 +8558,10 @@
         <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
         <v>0</v>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -8677,10 +8677,10 @@
         <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC69" t="n">
         <v>0</v>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -8751,13 +8751,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M70" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -8796,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CS Marítimo</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -8870,13 +8870,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="N71" t="n">
-        <v>3.53</v>
+        <v>4.43</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -8915,10 +8915,10 @@
         <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC71" t="n">
         <v>0</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -8963,12 +8963,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9082,12 +9082,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>CS Marítimo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9108,13 +9108,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="N73" t="n">
-        <v>4.43</v>
+        <v>3.53</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9153,10 +9153,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -10976,7 +10976,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Gouveia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Rebordosa</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11012,13 +11012,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11057,10 +11057,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11105,12 +11105,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Gouveia</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rebordosa</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -11131,13 +11131,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -11176,10 +11176,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>União Lamas</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Vila Real</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -11726,13 +11726,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -11771,10 +11771,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -11819,12 +11819,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.66</v>
+        <v>2.13</v>
       </c>
       <c r="M96" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="N96" t="n">
-        <v>2.87</v>
+        <v>3.84</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -11890,10 +11890,10 @@
         <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.96</v>
+        <v>2.15</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CF Os Belenenses</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -12678,13 +12678,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="M103" t="n">
-        <v>3.4</v>
+        <v>3.63</v>
       </c>
       <c r="N103" t="n">
-        <v>4.5</v>
+        <v>3.77</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -12723,10 +12723,10 @@
         <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC103" t="n">
         <v>0</v>
@@ -12761,7 +12761,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -12771,12 +12771,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>CF Os Belenenses</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -12797,13 +12797,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="M104" t="n">
-        <v>3.63</v>
+        <v>3.4</v>
       </c>
       <c r="N104" t="n">
-        <v>3.77</v>
+        <v>4.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -12842,10 +12842,10 @@
         <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -12999,7 +12999,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>União Lamas</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vila Real</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -13035,13 +13035,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -13080,10 +13080,10 @@
         <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14189,7 +14189,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -14199,12 +14199,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Celoricense</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mirandela</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -14225,13 +14225,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -14318,12 +14318,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AR São Martinho</t>
+          <t>Celoricense</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Mirandela</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>AR São Martinho</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -14463,13 +14463,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>3.36</v>
+        <v>2.19</v>
       </c>
       <c r="M130" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N130" t="n">
-        <v>2.06</v>
+        <v>3.25</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -15936,10 +15936,10 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -16460,12 +16460,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -16486,13 +16486,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>2.19</v>
+        <v>3.36</v>
       </c>
       <c r="M135" t="n">
-        <v>3.3</v>
+        <v>3.41</v>
       </c>
       <c r="N135" t="n">
-        <v>3.25</v>
+        <v>2.06</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -16531,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB135" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC135" t="n">
         <v>0</v>
@@ -17412,12 +17412,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -17438,13 +17438,13 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>1.63</v>
+        <v>3.42</v>
       </c>
       <c r="M143" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="N143" t="n">
-        <v>5.22</v>
+        <v>1.93</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -17483,10 +17483,10 @@
         <v>0</v>
       </c>
       <c r="AA143" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB143" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC143" t="n">
         <v>0</v>
@@ -17531,12 +17531,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -17557,13 +17557,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>3.42</v>
+        <v>1.63</v>
       </c>
       <c r="M144" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="N144" t="n">
-        <v>1.93</v>
+        <v>5.22</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -17602,10 +17602,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -17650,12 +17650,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -17676,13 +17676,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
       <c r="M145" t="n">
-        <v>3.83</v>
+        <v>3.28</v>
       </c>
       <c r="N145" t="n">
-        <v>4.58</v>
+        <v>2.57</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -17721,10 +17721,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB145" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -17769,12 +17769,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -17795,13 +17795,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>4.23</v>
+        <v>1.69</v>
       </c>
       <c r="M146" t="n">
-        <v>3.65</v>
+        <v>3.83</v>
       </c>
       <c r="N146" t="n">
-        <v>1.79</v>
+        <v>4.58</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -17840,10 +17840,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -18007,12 +18007,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -18033,13 +18033,13 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>2.83</v>
+        <v>4.23</v>
       </c>
       <c r="M148" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="N148" t="n">
-        <v>2.44</v>
+        <v>1.79</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -18078,10 +18078,10 @@
         <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB148" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC148" t="n">
         <v>0</v>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -18152,13 +18152,13 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="M149" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="N149" t="n">
-        <v>2.57</v>
+        <v>2.44</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -18197,10 +18197,10 @@
         <v>0</v>
       </c>
       <c r="AA149" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC149" t="n">
         <v>0</v>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -18483,12 +18483,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Santa Clara</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -18628,13 +18628,13 @@
         </is>
       </c>
       <c r="L153" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O153" t="n">
         <v>0</v>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -18840,12 +18840,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Santa Clara</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -18866,13 +18866,13 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="M155" t="n">
-        <v>2.98</v>
+        <v>3.14</v>
       </c>
       <c r="N155" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -18949,7 +18949,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -18959,12 +18959,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -18985,13 +18985,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -19068,7 +19068,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -19078,12 +19078,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -19104,13 +19104,13 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="N157" t="n">
-        <v>14.7</v>
+        <v>0</v>
       </c>
       <c r="O157" t="n">
         <v>0</v>
@@ -19187,7 +19187,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -19223,13 +19223,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="M158" t="n">
-        <v>5.23</v>
+        <v>5.65</v>
       </c>
       <c r="N158" t="n">
-        <v>7.75</v>
+        <v>14.7</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -19274,10 +19274,10 @@
         <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
         <v>0</v>
@@ -19306,7 +19306,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -19316,12 +19316,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1.21</v>
+        <v>1.39</v>
       </c>
       <c r="M159" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="N159" t="n">
-        <v>6.5</v>
+        <v>7.75</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -19387,16 +19387,16 @@
         <v>0</v>
       </c>
       <c r="AA159" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AB159" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC159" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="AD159" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AE159" t="n">
         <v>0</v>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -19435,12 +19435,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -19461,13 +19461,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -19506,16 +19506,16 @@
         <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE160" t="n">
         <v>0</v>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -19673,12 +19673,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -20056,13 +20056,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -20139,7 +20139,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -20149,12 +20149,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Ittihad Kalba</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -20175,13 +20175,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -20220,10 +20220,10 @@
         <v>0</v>
       </c>
       <c r="AA166" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB166" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC166" t="n">
         <v>0</v>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -20268,12 +20268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -20294,13 +20294,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -20387,12 +20387,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -20413,13 +20413,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="N168" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -20458,10 +20458,10 @@
         <v>0</v>
       </c>
       <c r="AA168" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC168" t="n">
         <v>0</v>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -20506,12 +20506,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -20532,13 +20532,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M169" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="N169" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -20577,10 +20577,10 @@
         <v>0</v>
       </c>
       <c r="AA169" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AB169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC169" t="n">
         <v>0</v>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -20625,12 +20625,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rennes</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -20651,13 +20651,13 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="N170" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O170" t="n">
         <v>0</v>
@@ -20734,7 +20734,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -20744,12 +20744,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Rennes</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -20770,13 +20770,13 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="M171" t="n">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="N171" t="n">
-        <v>4.84</v>
+        <v>4.62</v>
       </c>
       <c r="O171" t="n">
         <v>0</v>
@@ -20815,10 +20815,10 @@
         <v>0</v>
       </c>
       <c r="AA171" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB171" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC171" t="n">
         <v>0</v>
@@ -21101,12 +21101,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -21220,12 +21220,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -21696,12 +21696,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -21805,7 +21805,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -21815,12 +21815,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -21837,17 +21837,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L180" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N180" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -21924,7 +21924,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -21956,17 +21956,17 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -22172,12 +22172,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -22436,13 +22436,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -22529,12 +22529,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -22555,13 +22555,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M186" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="N186" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -22638,7 +22638,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -22648,12 +22648,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -22767,12 +22767,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -22793,13 +22793,13 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>4.26</v>
+        <v>2.75</v>
       </c>
       <c r="M188" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N188" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="O188" t="n">
         <v>0</v>
@@ -22876,7 +22876,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -22886,12 +22886,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -23124,12 +23124,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -23243,12 +23243,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -23362,12 +23362,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -23388,13 +23388,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="AA193" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB193" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC193" t="n">
         <v>0</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -23481,12 +23481,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -23507,13 +23507,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>4.8</v>
+        <v>4.26</v>
       </c>
       <c r="M194" t="n">
-        <v>3.56</v>
+        <v>4.1</v>
       </c>
       <c r="N194" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -23552,10 +23552,10 @@
         <v>0</v>
       </c>
       <c r="AA194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC194" t="n">
         <v>0</v>
@@ -23709,7 +23709,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -23719,12 +23719,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -23745,13 +23745,13 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O196" t="n">
         <v>0</v>
@@ -23790,10 +23790,10 @@
         <v>0</v>
       </c>
       <c r="AA196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB196" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC196" t="n">
         <v>0</v>
@@ -23828,7 +23828,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -23838,12 +23838,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -23864,13 +23864,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>3.01</v>
+        <v>2.68</v>
       </c>
       <c r="M197" t="n">
-        <v>3.84</v>
+        <v>3.17</v>
       </c>
       <c r="N197" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -23909,10 +23909,10 @@
         <v>0</v>
       </c>
       <c r="AA197" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB197" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC197" t="n">
         <v>0</v>
@@ -23947,7 +23947,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -23957,12 +23957,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -23983,13 +23983,13 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N198" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
         <v>0</v>
@@ -24542,7 +24542,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -24552,12 +24552,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>GD Estoril Praia</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -24578,13 +24578,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -24661,7 +24661,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -24671,12 +24671,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -24697,13 +24697,13 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O204" t="n">
         <v>0</v>
@@ -24780,7 +24780,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -24790,12 +24790,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>GD Estoril Praia</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -24816,13 +24816,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="M205" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="N205" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -25147,12 +25147,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -25173,13 +25173,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>2.68</v>
+        <v>2.15</v>
       </c>
       <c r="M208" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="N208" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -25494,7 +25494,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -25504,12 +25504,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -25530,13 +25530,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>3.39</v>
+        <v>2.3</v>
       </c>
       <c r="M211" t="n">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="N211" t="n">
-        <v>1.95</v>
+        <v>3.7</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -25575,10 +25575,10 @@
         <v>0</v>
       </c>
       <c r="AA211" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB211" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC211" t="n">
         <v>0</v>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -25623,12 +25623,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -25649,13 +25649,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.3</v>
+        <v>3.39</v>
       </c>
       <c r="M212" t="n">
-        <v>2.76</v>
+        <v>3.9</v>
       </c>
       <c r="N212" t="n">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -25694,10 +25694,10 @@
         <v>0</v>
       </c>
       <c r="AA212" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB212" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC212" t="n">
         <v>0</v>
@@ -26099,12 +26099,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -26125,13 +26125,13 @@
         </is>
       </c>
       <c r="L216" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="M216" t="n">
-        <v>3.96</v>
+        <v>3.68</v>
       </c>
       <c r="N216" t="n">
-        <v>5.16</v>
+        <v>4.62</v>
       </c>
       <c r="O216" t="n">
         <v>0</v>
@@ -26218,12 +26218,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -26244,13 +26244,13 @@
         </is>
       </c>
       <c r="L217" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="M217" t="n">
-        <v>3.68</v>
+        <v>3.96</v>
       </c>
       <c r="N217" t="n">
-        <v>4.62</v>
+        <v>5.16</v>
       </c>
       <c r="O217" t="n">
         <v>0</v>
@@ -26922,7 +26922,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -26932,12 +26932,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -26958,13 +26958,13 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
@@ -27041,7 +27041,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -27077,13 +27077,13 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>2.2</v>
+        <v>2.77</v>
       </c>
       <c r="M224" t="n">
-        <v>3.58</v>
+        <v>3.44</v>
       </c>
       <c r="N224" t="n">
-        <v>3.24</v>
+        <v>2.56</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
@@ -27122,10 +27122,10 @@
         <v>0</v>
       </c>
       <c r="AA224" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC224" t="n">
         <v>0</v>
@@ -27160,7 +27160,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -27196,13 +27196,13 @@
         </is>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M225" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N225" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
@@ -27241,10 +27241,10 @@
         <v>0</v>
       </c>
       <c r="AA225" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB225" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC225" t="n">
         <v>0</v>
@@ -27755,7 +27755,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -27765,12 +27765,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -27787,7 +27787,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -27884,12 +27884,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -27906,7 +27906,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -27993,7 +27993,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -28003,12 +28003,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -28112,7 +28112,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -28122,12 +28122,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G233" t="n">

--- a/jogos_2026-02-07.xlsx
+++ b/jogos_2026-02-07.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persik Kediri</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Persik Kediri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Sarıyer</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sarıyer</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="N25" t="n">
-        <v>3.83</v>
+        <v>4.31</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,22 +3753,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Persijap</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Bali United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Persijap</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,22 +4348,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.13</v>
+        <v>1.68</v>
       </c>
       <c r="M37" t="n">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="N37" t="n">
-        <v>3.35</v>
+        <v>4.74</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -4869,10 +4869,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB37" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4943,13 +4943,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3.65</v>
+        <v>2.13</v>
       </c>
       <c r="M38" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -4988,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5062,13 +5062,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.45</v>
+        <v>3.65</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5107,10 +5107,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5181,13 +5181,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5226,10 +5226,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5300,14 +5300,14 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="M41" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N41" t="n">
         <v>3.36</v>
       </c>
-      <c r="N41" t="n">
-        <